--- a/2026/BELGRANO 1646/Mayo/Mayo-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Mayo/Mayo-BLG1646.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A669151A-5916-4B9E-BA70-91708B65A0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8CA3D4-8F47-49EB-99FE-41E95D18CCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$123</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$125</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="148">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -420,36 +425,9 @@
     <t>BORRAR A MAURO MARANTE DE MAILS</t>
   </si>
   <si>
-    <t>Reemplazo Sr. Diego - Sra Monica</t>
-  </si>
-  <si>
-    <t>Pago mis cuentas 06/04</t>
-  </si>
-  <si>
-    <t>Citro Nicolas Hugo -  Pago de franquicia - Chevtrolex Onix 5A</t>
-  </si>
-  <si>
     <t>Debito 13/04</t>
   </si>
   <si>
-    <t>Remis Sr. Diego</t>
-  </si>
-  <si>
-    <t>Debito 29/04</t>
-  </si>
-  <si>
-    <t>Debito 01/04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel Villegas - Honorarios mediacion </t>
-  </si>
-  <si>
-    <t>Mediacion Sr. Simonassi</t>
-  </si>
-  <si>
-    <t>Sum mal cobrado UF 35</t>
-  </si>
-  <si>
     <t>VTO: 18/06</t>
   </si>
   <si>
@@ -495,9 +473,6 @@
     <t>Contessi - Reparacion de tensor trasero izquierdo de cabina de montacoches</t>
   </si>
   <si>
-    <t>Alterini Guido - Mantenimiento</t>
-  </si>
-  <si>
     <t>Urbeco - limpieza y desinfecion de tanques de agua potable, analisis y certificado corrrespondiente</t>
   </si>
   <si>
@@ -505,6 +480,33 @@
   </si>
   <si>
     <t>Casa Ruan - Compra de materiales electricos</t>
+  </si>
+  <si>
+    <t>Pago mis cuentas 06/05</t>
+  </si>
+  <si>
+    <t>Alterini Guido - Mantenimiento jardineria</t>
+  </si>
+  <si>
+    <t>Debito 22/05</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Para pileta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Articulos de limpieza </t>
+  </si>
+  <si>
+    <t>SA Seguridad - Emergencia porton rejas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servisur - cambio de luminarias </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>SGP colocacion de 4 cajas de paso en empalmes de luces de cantero patio SUM</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1088,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1216,7 +1218,6 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1284,6 +1285,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1370,86 +1388,82 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1529,9 +1543,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1569,9 +1583,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1604,9 +1618,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1639,9 +1670,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1815,184 +1863,184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N133"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N135"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="90"/>
-      <c r="B1" s="153" t="s">
+      <c r="B1" s="161" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="154"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="162"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
-      <c r="B2" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="108"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="107"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="108"/>
-    </row>
-    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="107"/>
+    </row>
+    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="108"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="107"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="107" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="108"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="106" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="106" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="107"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="108"/>
-    </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="111" t="s">
+      <c r="B6" s="106"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="107"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="110" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="112"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="110"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="111"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="109"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="78"/>
       <c r="B8" s="78"/>
       <c r="C8" s="78"/>
       <c r="D8" s="78"/>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="78"/>
       <c r="B9" s="78"/>
       <c r="C9" s="78"/>
       <c r="D9" s="78"/>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="78"/>
       <c r="B10" s="78"/>
       <c r="C10" s="78"/>
       <c r="D10" s="78"/>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="78"/>
       <c r="B11" s="78"/>
       <c r="C11" s="78"/>
       <c r="D11" s="78"/>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="78"/>
       <c r="B12" s="78"/>
       <c r="C12" s="78"/>
       <c r="D12" s="78"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="78"/>
       <c r="B13" s="78"/>
       <c r="C13" s="78"/>
       <c r="D13" s="78"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="78"/>
-      <c r="B14" s="157" t="s">
+      <c r="B14" s="165" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="158"/>
-      <c r="D14" s="159"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C14" s="166"/>
+      <c r="D14" s="167"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="78"/>
-      <c r="B15" s="160"/>
-      <c r="C15" s="161"/>
-      <c r="D15" s="162"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="168"/>
+      <c r="C15" s="169"/>
+      <c r="D15" s="170"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="78"/>
-      <c r="B16" s="160"/>
-      <c r="C16" s="161"/>
-      <c r="D16" s="162"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="168"/>
+      <c r="C16" s="169"/>
+      <c r="D16" s="170"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="78"/>
-      <c r="B17" s="163"/>
-      <c r="C17" s="164"/>
-      <c r="D17" s="165"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="171"/>
+      <c r="C17" s="172"/>
+      <c r="D17" s="173"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="78"/>
       <c r="B18" s="78"/>
       <c r="C18" s="78"/>
       <c r="D18" s="78"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="113"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="112"/>
       <c r="B19" s="78"/>
       <c r="C19" s="78"/>
       <c r="D19" s="78"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="78"/>
       <c r="B20" s="78"/>
       <c r="C20" s="78"/>
       <c r="D20" s="78"/>
     </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="114" t="s">
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="115"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="117"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="116"/>
       <c r="E21" s="83" t="s">
         <v>92</v>
       </c>
@@ -2000,120 +2048,116 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="118" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="117" t="s">
         <v>107</v>
       </c>
       <c r="B22" s="79" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C22" s="79"/>
-      <c r="D22" s="152"/>
+      <c r="D22" s="151"/>
       <c r="E22" s="82"/>
       <c r="F22" s="82"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="118" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="117" t="s">
         <v>96</v>
       </c>
       <c r="B23" s="79"/>
       <c r="C23" s="79"/>
-      <c r="D23" s="102">
-        <v>1667940.12</v>
+      <c r="D23" s="157">
+        <v>1575703.3</v>
       </c>
       <c r="E23" s="49">
         <f>D23*91.91%</f>
-        <v>1533003.7642919999</v>
+        <v>1448228.9030299999</v>
       </c>
       <c r="F23" s="49">
         <f>D23*8.09%</f>
-        <v>134936.35570800002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="118" t="s">
+        <v>127474.39697</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="117" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="79"/>
       <c r="C24" s="79"/>
-      <c r="D24" s="102">
-        <v>-362776.96</v>
+      <c r="D24" s="157">
+        <v>-342715.56</v>
       </c>
       <c r="E24" s="49">
         <f t="shared" ref="E24:E26" si="0">D24*91.91%</f>
-        <v>-333428.30393599998</v>
+        <v>-314989.87119599996</v>
       </c>
       <c r="F24" s="49">
         <f t="shared" ref="F24:F26" si="1">D24*8.09%</f>
-        <v>-29348.656064000003</v>
+        <v>-27725.688804000001</v>
       </c>
       <c r="G24" s="34"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="118" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="117" t="s">
         <v>84</v>
       </c>
       <c r="B25" s="79"/>
       <c r="C25" s="79"/>
-      <c r="D25" s="102">
-        <v>0.84</v>
+      <c r="D25" s="157">
+        <v>0.16</v>
       </c>
       <c r="E25" s="49">
         <f t="shared" si="0"/>
-        <v>0.77204399999999995</v>
+        <v>0.14705599999999999</v>
       </c>
       <c r="F25" s="49">
         <f t="shared" si="1"/>
-        <v>6.7956000000000003E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="118" t="s">
-        <v>124</v>
-      </c>
+        <v>1.2944000000000001E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="117"/>
       <c r="B26" s="79"/>
       <c r="C26" s="79"/>
-      <c r="D26" s="102">
-        <v>20000</v>
-      </c>
+      <c r="D26" s="102"/>
       <c r="E26" s="49">
         <f t="shared" si="0"/>
-        <v>18382</v>
+        <v>0</v>
       </c>
       <c r="F26" s="49">
         <f t="shared" si="1"/>
-        <v>1618</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="119" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="119"/>
-      <c r="C27" s="119"/>
+      <c r="B27" s="118"/>
+      <c r="C27" s="118"/>
       <c r="D27" s="33">
         <f>SUM(D23:D26)</f>
-        <v>1325164.0000000002</v>
+        <v>1232987.8999999999</v>
       </c>
       <c r="E27" s="33">
         <f>SUM(E23:E26)</f>
-        <v>1217958.2323999999</v>
+        <v>1133239.1788900001</v>
       </c>
       <c r="F27" s="33">
         <f>SUM(F23:F26)</f>
-        <v>107205.76760000001</v>
+        <v>99748.721109999999</v>
       </c>
       <c r="G27" s="34">
         <f>E27+F27</f>
-        <v>1325163.9999999998</v>
+        <v>1232987.9000000001</v>
       </c>
       <c r="H27" s="61" t="str">
         <f>IF(D27=G27, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="120" t="s">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="119" t="s">
         <v>82</v>
       </c>
       <c r="B28" s="79"/>
@@ -2131,8 +2175,8 @@
       </c>
       <c r="H28" s="61"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="120"/>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="119"/>
       <c r="B29" s="79"/>
       <c r="C29" s="79"/>
       <c r="D29" s="102">
@@ -2148,8 +2192,8 @@
       </c>
       <c r="H29" s="61"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="120"/>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="119"/>
       <c r="B30" s="79"/>
       <c r="C30" s="79"/>
       <c r="D30" s="102"/>
@@ -2157,8 +2201,8 @@
       <c r="F30" s="3"/>
       <c r="H30" s="61"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="120"/>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="119"/>
       <c r="B31" s="79"/>
       <c r="C31" s="79"/>
       <c r="D31" s="102"/>
@@ -2166,12 +2210,12 @@
       <c r="F31" s="3"/>
       <c r="H31" s="61"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="119" t="s">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="118" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="119"/>
-      <c r="C32" s="119"/>
+      <c r="B32" s="118"/>
+      <c r="C32" s="118"/>
       <c r="D32" s="33">
         <f>SUM(D28:D30)</f>
         <v>0</v>
@@ -2193,26 +2237,22 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="120" t="s">
-        <v>120</v>
-      </c>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="119"/>
       <c r="B33" s="79"/>
       <c r="C33" s="79"/>
-      <c r="D33" s="103">
-        <v>84000</v>
-      </c>
+      <c r="D33" s="103"/>
       <c r="E33" s="49">
         <f>D33*91.91%</f>
-        <v>77204.399999999994</v>
+        <v>0</v>
       </c>
       <c r="F33" s="49">
         <f>D33*8.09%</f>
-        <v>6795.6</v>
+        <v>0</v>
       </c>
       <c r="H33" s="61"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="79"/>
       <c r="B34" s="79"/>
       <c r="C34" s="79"/>
@@ -2227,8 +2267,8 @@
       </c>
       <c r="H34" s="61"/>
     </row>
-    <row r="35" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="120"/>
+    <row r="35" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="119"/>
       <c r="B35" s="79"/>
       <c r="C35" s="79"/>
       <c r="D35" s="102"/>
@@ -2242,28 +2282,28 @@
       </c>
       <c r="H35" s="61"/>
     </row>
-    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="119" t="s">
+    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="118" t="s">
         <v>97</v>
       </c>
-      <c r="B36" s="119"/>
-      <c r="C36" s="119"/>
+      <c r="B36" s="118"/>
+      <c r="C36" s="118"/>
       <c r="D36" s="33">
         <f>SUM(D29:D35)</f>
-        <v>84000</v>
+        <v>0</v>
       </c>
       <c r="E36" s="33">
         <f t="shared" ref="E36" si="5">SUM(E29:E35)</f>
-        <v>77204.399999999994</v>
+        <v>0</v>
       </c>
       <c r="F36" s="41">
         <f>E36*8.09%</f>
-        <v>6245.8359599999994</v>
+        <v>0</v>
       </c>
       <c r="H36" s="61"/>
     </row>
-    <row r="37" spans="1:8" ht="0.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="121"/>
+    <row r="37" spans="1:8" ht="0.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="120"/>
       <c r="B37" s="101"/>
       <c r="C37" s="101"/>
       <c r="D37" s="102"/>
@@ -2271,8 +2311,8 @@
       <c r="F37" s="42"/>
       <c r="H37" s="61"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="121"/>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="120"/>
       <c r="B38" s="101"/>
       <c r="C38" s="101"/>
       <c r="D38" s="102"/>
@@ -2280,21 +2320,21 @@
       <c r="F38" s="42"/>
       <c r="H38" s="61"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="101"/>
       <c r="B39" s="101"/>
-      <c r="C39" s="122"/>
+      <c r="C39" s="121"/>
       <c r="D39" s="102"/>
       <c r="E39" s="42"/>
       <c r="F39" s="42"/>
       <c r="H39" s="61"/>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="119" t="s">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="118" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="119"/>
-      <c r="C40" s="119"/>
+      <c r="B40" s="118"/>
+      <c r="C40" s="118"/>
       <c r="D40" s="33"/>
       <c r="E40" s="36">
         <f>SUM(D37:D39)</f>
@@ -2306,7 +2346,7 @@
       </c>
       <c r="H40" s="61"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="79"/>
       <c r="B41" s="79"/>
       <c r="C41" s="101"/>
@@ -2320,12 +2360,12 @@
       <c r="F41" s="49"/>
       <c r="H41" s="61"/>
     </row>
-    <row r="42" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="119" t="s">
+    <row r="42" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="118" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="119"/>
-      <c r="C42" s="119"/>
+      <c r="B42" s="118"/>
+      <c r="C42" s="118"/>
       <c r="D42" s="33">
         <f>SUM(D41:D41)</f>
         <v>0</v>
@@ -2344,8 +2384,8 @@
       </c>
       <c r="H42" s="61"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="120" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="119" t="s">
         <v>4</v>
       </c>
       <c r="B43" s="79"/>
@@ -2355,13 +2395,13 @@
       <c r="F43" s="26"/>
       <c r="H43" s="61"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="120" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="119" t="s">
         <v>110</v>
       </c>
       <c r="B44" s="79"/>
       <c r="C44" s="101"/>
-      <c r="D44" s="37">
+      <c r="D44" s="155">
         <v>6642</v>
       </c>
       <c r="E44" s="49">
@@ -2374,15 +2414,15 @@
       </c>
       <c r="H44" s="61"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="120" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="119" t="s">
         <v>5</v>
       </c>
       <c r="B45" s="79" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C45" s="79"/>
-      <c r="D45" s="207">
+      <c r="D45" s="155">
         <f>75057.3+8339.7+151650.1</f>
         <v>235047.1</v>
       </c>
@@ -2396,15 +2436,15 @@
       </c>
       <c r="H45" s="61"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="120" t="s">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="119" t="s">
         <v>103</v>
       </c>
       <c r="B46" s="101" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="C46" s="79"/>
-      <c r="D46" s="207">
+      <c r="D46" s="155">
         <v>739569.96</v>
       </c>
       <c r="E46" s="49">
@@ -2417,12 +2457,12 @@
       </c>
       <c r="H46" s="61"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="119" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="123"/>
-      <c r="C47" s="123"/>
+      <c r="B47" s="122"/>
+      <c r="C47" s="122"/>
       <c r="D47" s="33">
         <f>SUM(D44:D46)</f>
         <v>981259.05999999994</v>
@@ -2444,7 +2484,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="79" t="s">
         <v>7</v>
       </c>
@@ -2455,13 +2495,13 @@
       <c r="F48" s="3"/>
       <c r="H48" s="61"/>
     </row>
-    <row r="49" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="124" t="s">
+    <row r="49" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="123" t="s">
         <v>105</v>
       </c>
       <c r="B49" s="79"/>
       <c r="C49" s="79"/>
-      <c r="D49" s="207">
+      <c r="D49" s="155">
         <v>434000</v>
       </c>
       <c r="E49" s="60">
@@ -2483,13 +2523,13 @@
       </c>
       <c r="J49" s="76"/>
     </row>
-    <row r="50" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="124" t="s">
-        <v>144</v>
+    <row r="50" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="123" t="s">
+        <v>135</v>
       </c>
       <c r="B50" s="79"/>
       <c r="C50" s="79"/>
-      <c r="D50" s="207">
+      <c r="D50" s="155">
         <v>380000</v>
       </c>
       <c r="E50" s="60">
@@ -2502,41 +2542,41 @@
       <c r="I50" s="76"/>
       <c r="J50" s="76"/>
     </row>
-    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="118" t="s">
+    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="127"/>
+      <c r="B51" s="126"/>
       <c r="C51" s="79"/>
-      <c r="D51" s="207">
-        <v>211387.67</v>
+      <c r="D51" s="155">
+        <v>255779</v>
       </c>
       <c r="E51" s="60">
-        <f t="shared" ref="E51:E58" si="7">D51*91.91%</f>
-        <v>194286.40749700001</v>
+        <f t="shared" ref="E51:E59" si="7">D51*91.91%</f>
+        <v>235086.47889999999</v>
       </c>
       <c r="F51" s="49">
-        <f t="shared" ref="F51:F58" si="8">D51*8.09%</f>
-        <v>17101.262503000002</v>
+        <f t="shared" ref="F51:F59" si="8">D51*8.09%</f>
+        <v>20692.521099999998</v>
       </c>
       <c r="G51" s="34">
-        <f t="shared" ref="G51:G68" si="9">D51</f>
-        <v>211387.67</v>
+        <f t="shared" ref="G51:G70" si="9">D51</f>
+        <v>255779</v>
       </c>
       <c r="H51" s="67">
-        <f t="shared" ref="H51:H68" si="10">E51+F51</f>
-        <v>211387.67</v>
+        <f t="shared" ref="H51:H70" si="10">E51+F51</f>
+        <v>255779</v>
       </c>
       <c r="I51" s="76"/>
       <c r="J51" s="76"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="120" t="s">
-        <v>143</v>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="119" t="s">
+        <v>134</v>
       </c>
       <c r="B52" s="79"/>
       <c r="C52" s="79"/>
-      <c r="D52" s="207">
+      <c r="D52" s="155">
         <v>59169</v>
       </c>
       <c r="E52" s="60">
@@ -2558,107 +2598,103 @@
       <c r="I52" s="76"/>
       <c r="J52" s="76"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="120" t="s">
-        <v>133</v>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="119" t="s">
+        <v>144</v>
       </c>
       <c r="B53" s="79"/>
       <c r="C53" s="79"/>
-      <c r="D53" s="37">
-        <v>192118.96</v>
+      <c r="D53" s="155">
+        <v>108900</v>
       </c>
       <c r="E53" s="60">
-        <f t="shared" ref="E53" si="11">D53*91.91%</f>
-        <v>176576.53613599998</v>
+        <f t="shared" si="7"/>
+        <v>100089.98999999999</v>
       </c>
       <c r="F53" s="49">
-        <f t="shared" ref="F53" si="12">D53*8.09%</f>
-        <v>15542.423863999999</v>
-      </c>
-      <c r="G53" s="34">
-        <f t="shared" ref="G53" si="13">D53</f>
-        <v>192118.96</v>
-      </c>
-      <c r="H53" s="67">
-        <f t="shared" ref="H53" si="14">E53+F53</f>
-        <v>192118.96</v>
-      </c>
+        <f t="shared" si="8"/>
+        <v>8810.01</v>
+      </c>
+      <c r="G53" s="34"/>
+      <c r="H53" s="67"/>
       <c r="I53" s="76"/>
       <c r="J53" s="76"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="120" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54" s="79" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" s="79" t="s">
-        <v>126</v>
-      </c>
-      <c r="D54" s="37">
-        <v>129320</v>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" s="79"/>
+      <c r="C54" s="79"/>
+      <c r="D54" s="155">
+        <v>205404</v>
       </c>
       <c r="E54" s="60">
-        <f>D54*91.91%</f>
-        <v>118858.01199999999</v>
+        <f t="shared" ref="E54" si="11">D54*91.91%</f>
+        <v>188786.81639999998</v>
       </c>
       <c r="F54" s="49">
-        <f t="shared" si="8"/>
-        <v>10461.987999999999</v>
+        <f t="shared" ref="F54" si="12">D54*8.09%</f>
+        <v>16617.1836</v>
       </c>
       <c r="G54" s="34">
-        <f t="shared" si="9"/>
-        <v>129320</v>
+        <f t="shared" ref="G54" si="13">D54</f>
+        <v>205404</v>
       </c>
       <c r="H54" s="67">
-        <f>E54+F54</f>
-        <v>129319.99999999999</v>
-      </c>
-      <c r="I54" s="76">
-        <f t="shared" ref="I54:I68" si="15">H54-D54</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="76">
-        <f t="shared" ref="J54:J68" si="16">G54-D54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="120" t="s">
+        <f t="shared" ref="H54" si="14">E54+F54</f>
+        <v>205403.99999999997</v>
+      </c>
+      <c r="I54" s="76"/>
+      <c r="J54" s="76"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="119" t="s">
         <v>9</v>
       </c>
       <c r="B55" s="79" t="s">
         <v>109</v>
       </c>
       <c r="C55" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="D55" s="37">
-        <v>129320</v>
+        <v>141</v>
+      </c>
+      <c r="D55" s="155">
+        <v>129315.21</v>
       </c>
       <c r="E55" s="60">
         <f>D55*91.91%</f>
-        <v>118858.01199999999</v>
+        <v>118853.609511</v>
       </c>
       <c r="F55" s="49">
         <f t="shared" si="8"/>
-        <v>10461.987999999999</v>
-      </c>
-      <c r="G55" s="34"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="76"/>
-      <c r="J55" s="76"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="120" t="s">
+        <v>10461.600489</v>
+      </c>
+      <c r="G55" s="34">
+        <f t="shared" si="9"/>
+        <v>129315.21</v>
+      </c>
+      <c r="H55" s="67">
+        <f>E55+F55</f>
+        <v>129315.21</v>
+      </c>
+      <c r="I55" s="76">
+        <f t="shared" ref="I55:I70" si="15">H55-D55</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="76">
+        <f t="shared" ref="J55:J70" si="16">G55-D55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="119" t="s">
         <v>11</v>
       </c>
       <c r="B56" s="101" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C56" s="79"/>
-      <c r="D56" s="207">
+      <c r="D56" s="155">
         <v>353513.62</v>
       </c>
       <c r="E56" s="60">
@@ -2686,13 +2722,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="120" t="s">
-        <v>146</v>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="119" t="s">
+        <v>136</v>
       </c>
       <c r="B57" s="79"/>
       <c r="C57" s="79"/>
-      <c r="D57" s="207">
+      <c r="D57" s="155">
         <v>544500</v>
       </c>
       <c r="E57" s="60">
@@ -2714,30 +2750,30 @@
       <c r="I57" s="76"/>
       <c r="J57" s="76"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="121" t="s">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="120" t="s">
         <v>10</v>
       </c>
       <c r="B58" s="101"/>
       <c r="C58" s="101"/>
-      <c r="D58" s="207">
-        <v>37171.58</v>
+      <c r="D58" s="155">
+        <v>37141.58</v>
       </c>
       <c r="E58" s="60">
         <f t="shared" si="7"/>
-        <v>34164.399178</v>
+        <v>34136.826177999996</v>
       </c>
       <c r="F58" s="49">
         <f t="shared" si="8"/>
-        <v>3007.1808220000003</v>
+        <v>3004.7538220000001</v>
       </c>
       <c r="G58" s="34">
         <f t="shared" si="9"/>
-        <v>37171.58</v>
+        <v>37141.58</v>
       </c>
       <c r="H58" s="67">
         <f t="shared" si="10"/>
-        <v>37171.58</v>
+        <v>37141.579999999994</v>
       </c>
       <c r="I58" s="76">
         <f t="shared" si="15"/>
@@ -2748,133 +2784,133 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="128" t="s">
-        <v>134</v>
-      </c>
-      <c r="B59" s="143"/>
-      <c r="C59" s="144"/>
-      <c r="D59" s="207">
-        <v>62000</v>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="120" t="s">
+        <v>147</v>
+      </c>
+      <c r="B59" s="141"/>
+      <c r="C59" s="216"/>
+      <c r="D59" s="155">
+        <v>150000</v>
       </c>
       <c r="E59" s="60">
-        <f t="shared" ref="E59:E60" si="17">D59</f>
-        <v>62000</v>
-      </c>
-      <c r="F59" s="49"/>
+        <f t="shared" si="7"/>
+        <v>137865</v>
+      </c>
+      <c r="F59" s="49">
+        <f t="shared" si="8"/>
+        <v>12135</v>
+      </c>
       <c r="G59" s="34">
         <f t="shared" si="9"/>
+        <v>150000</v>
+      </c>
+      <c r="H59" s="67">
+        <f t="shared" si="10"/>
+        <v>150000</v>
+      </c>
+      <c r="I59" s="76"/>
+      <c r="J59" s="76"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="127" t="s">
+        <v>125</v>
+      </c>
+      <c r="B60" s="142"/>
+      <c r="C60" s="143"/>
+      <c r="D60" s="155">
         <v>62000</v>
       </c>
-      <c r="H59" s="67"/>
-      <c r="I59" s="76"/>
-      <c r="J59" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="210" t="s">
-        <v>145</v>
-      </c>
-      <c r="B60" s="143"/>
-      <c r="C60" s="144"/>
-      <c r="D60" s="209">
-        <v>90000</v>
-      </c>
       <c r="E60" s="60">
-        <f t="shared" si="17"/>
-        <v>90000</v>
+        <f t="shared" ref="E60:E61" si="17">D60</f>
+        <v>62000</v>
       </c>
       <c r="F60" s="49"/>
       <c r="G60" s="34">
         <f t="shared" si="9"/>
-        <v>90000</v>
+        <v>62000</v>
       </c>
       <c r="H60" s="67"/>
       <c r="I60" s="76"/>
-      <c r="J60" s="76"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="140" t="s">
-        <v>142</v>
-      </c>
-      <c r="B61" s="129"/>
-      <c r="C61" s="130"/>
-      <c r="D61" s="207">
-        <v>55000</v>
+      <c r="J60" s="76">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="156" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" s="142"/>
+      <c r="C61" s="143"/>
+      <c r="D61" s="155">
+        <v>90000</v>
       </c>
       <c r="E61" s="60">
-        <f>D61</f>
-        <v>55000</v>
+        <f t="shared" si="17"/>
+        <v>90000</v>
       </c>
       <c r="F61" s="49"/>
       <c r="G61" s="34">
         <f t="shared" si="9"/>
+        <v>90000</v>
+      </c>
+      <c r="H61" s="67"/>
+      <c r="I61" s="76"/>
+      <c r="J61" s="76"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="139" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" s="128"/>
+      <c r="C62" s="129"/>
+      <c r="D62" s="155">
         <v>55000</v>
       </c>
-      <c r="H61" s="67">
-        <f t="shared" si="10"/>
+      <c r="E62" s="60">
+        <f t="shared" ref="E62:E67" si="18">D62</f>
         <v>55000</v>
-      </c>
-      <c r="I61" s="76">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="180" t="s">
-        <v>138</v>
-      </c>
-      <c r="B62" s="181"/>
-      <c r="C62" s="182"/>
-      <c r="D62" s="207">
-        <v>420000</v>
-      </c>
-      <c r="E62" s="60">
-        <f>D62</f>
-        <v>420000</v>
       </c>
       <c r="F62" s="49"/>
       <c r="G62" s="34">
         <f t="shared" si="9"/>
-        <v>420000</v>
+        <v>55000</v>
       </c>
       <c r="H62" s="67">
         <f t="shared" si="10"/>
-        <v>420000</v>
-      </c>
-      <c r="I62" s="76"/>
+        <v>55000</v>
+      </c>
+      <c r="I62" s="76">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="J62" s="76">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="208" t="s">
-        <v>139</v>
-      </c>
-      <c r="B63" s="178"/>
-      <c r="C63" s="179"/>
-      <c r="D63" s="207">
-        <v>90000</v>
+    <row r="63" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="188" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" s="189"/>
+      <c r="C63" s="190"/>
+      <c r="D63" s="155">
+        <v>420000</v>
       </c>
       <c r="E63" s="60">
-        <f>D63</f>
-        <v>90000</v>
+        <f t="shared" si="18"/>
+        <v>420000</v>
       </c>
       <c r="F63" s="49"/>
       <c r="G63" s="34">
         <f t="shared" si="9"/>
-        <v>90000</v>
+        <v>420000</v>
       </c>
       <c r="H63" s="67">
         <f t="shared" si="10"/>
-        <v>90000</v>
+        <v>420000</v>
       </c>
       <c r="I63" s="76"/>
       <c r="J63" s="76">
@@ -2882,139 +2918,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="208" t="s">
-        <v>147</v>
-      </c>
-      <c r="B64" s="178"/>
-      <c r="C64" s="179"/>
-      <c r="D64" s="207">
-        <v>70000</v>
+    <row r="64" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="191" t="s">
+        <v>130</v>
+      </c>
+      <c r="B64" s="186"/>
+      <c r="C64" s="187"/>
+      <c r="D64" s="155">
+        <v>90000</v>
       </c>
       <c r="E64" s="60">
-        <f>D64</f>
-        <v>70000</v>
+        <f t="shared" si="18"/>
+        <v>90000</v>
       </c>
       <c r="F64" s="49"/>
       <c r="G64" s="34">
         <f t="shared" si="9"/>
-        <v>70000</v>
-      </c>
-      <c r="H64" s="67"/>
+        <v>90000</v>
+      </c>
+      <c r="H64" s="67">
+        <f t="shared" si="10"/>
+        <v>90000</v>
+      </c>
       <c r="I64" s="76"/>
       <c r="J64" s="76">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="180" t="s">
-        <v>140</v>
-      </c>
-      <c r="B65" s="181"/>
-      <c r="C65" s="182"/>
-      <c r="D65" s="207">
-        <v>33000</v>
+    <row r="65" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="154" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" s="152"/>
+      <c r="C65" s="153"/>
+      <c r="D65" s="155">
+        <v>120000</v>
       </c>
       <c r="E65" s="60">
-        <f>D65</f>
-        <v>33000</v>
-      </c>
-      <c r="F65" s="49">
-        <v>0</v>
-      </c>
+        <f t="shared" si="18"/>
+        <v>120000</v>
+      </c>
+      <c r="F65" s="49"/>
       <c r="G65" s="34">
-        <f t="shared" ref="G65" si="18">D65</f>
-        <v>33000</v>
-      </c>
-      <c r="H65" s="67">
-        <f t="shared" ref="H65" si="19">E65+F65</f>
-        <v>33000</v>
-      </c>
+        <f t="shared" si="9"/>
+        <v>120000</v>
+      </c>
+      <c r="H65" s="67"/>
       <c r="I65" s="76"/>
-      <c r="J65" s="76"/>
-    </row>
-    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="180" t="s">
-        <v>148</v>
-      </c>
-      <c r="B66" s="181"/>
-      <c r="C66" s="182"/>
-      <c r="D66" s="207">
-        <v>25200</v>
+      <c r="J65" s="76">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="191" t="s">
+        <v>137</v>
+      </c>
+      <c r="B66" s="186"/>
+      <c r="C66" s="187"/>
+      <c r="D66" s="155">
+        <v>70000</v>
       </c>
       <c r="E66" s="60">
-        <f t="shared" ref="E66:E68" si="20">D66</f>
-        <v>25200</v>
+        <f t="shared" si="18"/>
+        <v>70000</v>
       </c>
       <c r="F66" s="49"/>
       <c r="G66" s="34">
         <f t="shared" si="9"/>
-        <v>25200</v>
-      </c>
-      <c r="H66" s="67">
-        <f t="shared" si="10"/>
-        <v>25200</v>
-      </c>
-      <c r="I66" s="76">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
+        <v>70000</v>
+      </c>
+      <c r="H66" s="67"/>
+      <c r="I66" s="76"/>
       <c r="J66" s="76">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="B67" s="125" t="s">
-        <v>135</v>
-      </c>
-      <c r="C67" s="141"/>
-      <c r="D67" s="37">
-        <v>101783</v>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="188" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" s="189"/>
+      <c r="C67" s="190"/>
+      <c r="D67" s="155">
+        <v>33000</v>
       </c>
       <c r="E67" s="60">
-        <f t="shared" si="20"/>
-        <v>101783</v>
-      </c>
-      <c r="F67" s="49"/>
+        <f t="shared" si="18"/>
+        <v>33000</v>
+      </c>
+      <c r="F67" s="49">
+        <v>0</v>
+      </c>
       <c r="G67" s="34">
-        <f t="shared" si="9"/>
-        <v>101783</v>
+        <f t="shared" ref="G67" si="19">D67</f>
+        <v>33000</v>
       </c>
       <c r="H67" s="67">
-        <f t="shared" si="10"/>
-        <v>101783</v>
-      </c>
-      <c r="I67" s="76">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="177"/>
-      <c r="B68" s="178"/>
-      <c r="C68" s="179"/>
-      <c r="D68" s="37"/>
+        <f t="shared" ref="H67" si="20">E67+F67</f>
+        <v>33000</v>
+      </c>
+      <c r="I67" s="76"/>
+      <c r="J67" s="76"/>
+    </row>
+    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="188" t="s">
+        <v>138</v>
+      </c>
+      <c r="B68" s="189"/>
+      <c r="C68" s="190"/>
+      <c r="D68" s="155">
+        <v>25200</v>
+      </c>
       <c r="E68" s="60">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f t="shared" ref="E68:E70" si="21">D68</f>
+        <v>25200</v>
       </c>
       <c r="F68" s="49"/>
       <c r="G68" s="34">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="H68" s="67">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="I68" s="76">
         <f t="shared" si="15"/>
@@ -3025,763 +3054,818 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="119" t="s">
+    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="B69" s="124" t="s">
+        <v>126</v>
+      </c>
+      <c r="C69" s="140"/>
+      <c r="D69" s="155">
+        <v>103395</v>
+      </c>
+      <c r="E69" s="60">
+        <f t="shared" si="21"/>
+        <v>103395</v>
+      </c>
+      <c r="F69" s="49"/>
+      <c r="G69" s="34">
+        <f t="shared" si="9"/>
+        <v>103395</v>
+      </c>
+      <c r="H69" s="67">
+        <f t="shared" si="10"/>
+        <v>103395</v>
+      </c>
+      <c r="I69" s="76">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="76">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="185"/>
+      <c r="B70" s="186"/>
+      <c r="C70" s="187"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="60">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="49"/>
+      <c r="G70" s="34">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="67">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I70" s="76">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="76">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="B69" s="123"/>
-      <c r="C69" s="123"/>
-      <c r="D69" s="33">
-        <f>SUM(D49:D68)</f>
-        <v>3417483.83</v>
-      </c>
-      <c r="E69" s="33">
-        <f>SUM(E49:E68)</f>
-        <v>3283472.9128529998</v>
-      </c>
-      <c r="F69" s="33">
-        <f>SUM(F49:F68)</f>
-        <v>134010.917147</v>
-      </c>
-      <c r="G69" s="34">
-        <f>E69+F69</f>
-        <v>3417483.8299999996</v>
-      </c>
-      <c r="H69" s="61" t="str">
-        <f>IF(D69=G69, "", "Error")</f>
+      <c r="B71" s="122"/>
+      <c r="C71" s="122"/>
+      <c r="D71" s="33">
+        <f>SUM(D49:D70)</f>
+        <v>3726317.41</v>
+      </c>
+      <c r="E71" s="33">
+        <f>SUM(E49:E70)</f>
+        <v>3577160.2670309995</v>
+      </c>
+      <c r="F71" s="33">
+        <f>SUM(F49:F70)</f>
+        <v>149157.14296900001</v>
+      </c>
+      <c r="G71" s="34">
+        <f>E71+F71</f>
+        <v>3726317.4099999997</v>
+      </c>
+      <c r="H71" s="61" t="str">
+        <f>IF(D71=G71, "", "Error")</f>
         <v/>
       </c>
-      <c r="I69" s="76">
-        <f>D69-G69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="79"/>
-      <c r="B70" s="79"/>
-      <c r="C70" s="79"/>
-      <c r="D70" s="104"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="3"/>
-      <c r="H70" s="61"/>
-    </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="79"/>
-      <c r="B71" s="79"/>
-      <c r="C71" s="79"/>
-      <c r="D71" s="104"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="3"/>
-      <c r="H71" s="61"/>
-    </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I71" s="76">
+        <f>D71-G71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="79"/>
       <c r="B72" s="79"/>
       <c r="C72" s="79"/>
       <c r="D72" s="104"/>
-      <c r="E72" s="38"/>
+      <c r="E72" s="39"/>
       <c r="F72" s="3"/>
       <c r="H72" s="61"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="121"/>
-      <c r="B73" s="101"/>
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="79"/>
+      <c r="B73" s="79"/>
       <c r="C73" s="79"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="60">
-        <f>D73*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F73" s="49">
-        <f>D73*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G73" s="66"/>
+      <c r="D73" s="104"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="3"/>
       <c r="H73" s="61"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="101"/>
-      <c r="B74" s="142"/>
-      <c r="C74" s="126"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="60">
-        <f>D74</f>
-        <v>0</v>
-      </c>
-      <c r="F74" s="49">
-        <v>0</v>
-      </c>
-      <c r="G74" s="66"/>
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="79"/>
+      <c r="B74" s="79"/>
+      <c r="C74" s="79"/>
+      <c r="D74" s="104"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="3"/>
       <c r="H74" s="61"/>
     </row>
-    <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="119" t="s">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="120" t="s">
+        <v>143</v>
+      </c>
+      <c r="B75" s="101"/>
+      <c r="C75" s="79"/>
+      <c r="D75" s="155">
+        <v>252200</v>
+      </c>
+      <c r="E75" s="60">
+        <f>D75*91.91%</f>
+        <v>231797.02</v>
+      </c>
+      <c r="F75" s="49">
+        <f>D75*8.09%</f>
+        <v>20402.98</v>
+      </c>
+      <c r="G75" s="66"/>
+      <c r="H75" s="61"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="120" t="s">
+        <v>143</v>
+      </c>
+      <c r="B76" s="141"/>
+      <c r="C76" s="125"/>
+      <c r="D76" s="155">
+        <v>155650</v>
+      </c>
+      <c r="E76" s="60">
+        <f>D76*91.91%</f>
+        <v>143057.91499999998</v>
+      </c>
+      <c r="F76" s="49">
+        <f>D76*8.09%</f>
+        <v>12592.084999999999</v>
+      </c>
+      <c r="G76" s="66"/>
+      <c r="H76" s="61"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="101" t="s">
+        <v>142</v>
+      </c>
+      <c r="B77" s="141"/>
+      <c r="C77" s="125"/>
+      <c r="D77" s="155">
+        <v>112800</v>
+      </c>
+      <c r="E77" s="60">
+        <f>D77</f>
+        <v>112800</v>
+      </c>
+      <c r="F77" s="49">
+        <v>0</v>
+      </c>
+      <c r="G77" s="66"/>
+      <c r="H77" s="61"/>
+    </row>
+    <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="B75" s="119"/>
-      <c r="C75" s="119"/>
-      <c r="D75" s="33">
-        <f>SUM(D73:D74)</f>
-        <v>0</v>
-      </c>
-      <c r="E75" s="33">
-        <f>SUM(E73:E74)</f>
-        <v>0</v>
-      </c>
-      <c r="F75" s="33">
-        <f>SUM(F73:F74)</f>
-        <v>0</v>
-      </c>
-      <c r="G75" s="34">
-        <f>E75+F75</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="61" t="str">
-        <f>IF(D75=G75, "", "Error")</f>
+      <c r="B78" s="118"/>
+      <c r="C78" s="118"/>
+      <c r="D78" s="33">
+        <f>SUM(D75:D77)</f>
+        <v>520650</v>
+      </c>
+      <c r="E78" s="33">
+        <f>SUM(E75:E77)</f>
+        <v>487654.93499999994</v>
+      </c>
+      <c r="F78" s="33">
+        <f>SUM(F75:F77)</f>
+        <v>32995.065000000002</v>
+      </c>
+      <c r="G78" s="34">
+        <f>E78+F78</f>
+        <v>520649.99999999994</v>
+      </c>
+      <c r="H78" s="61" t="str">
+        <f>IF(D78=G78, "", "Error")</f>
         <v/>
       </c>
-      <c r="J75" s="34"/>
-    </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="79"/>
-      <c r="B76" s="79"/>
-      <c r="C76" s="79"/>
-      <c r="D76" s="104"/>
-      <c r="E76" s="39"/>
-      <c r="F76" s="3"/>
-      <c r="H76" s="61"/>
-    </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="79"/>
-      <c r="B77" s="79"/>
-      <c r="C77" s="79"/>
-      <c r="D77" s="104"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="3"/>
-      <c r="H77" s="61"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="120" t="s">
+      <c r="J78" s="34"/>
+    </row>
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="79"/>
+      <c r="B79" s="79"/>
+      <c r="C79" s="79"/>
+      <c r="D79" s="104"/>
+      <c r="E79" s="39"/>
+      <c r="F79" s="3"/>
+      <c r="H79" s="61"/>
+    </row>
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="79"/>
+      <c r="B80" s="79"/>
+      <c r="C80" s="79"/>
+      <c r="D80" s="104"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="3"/>
+      <c r="H80" s="61"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="119" t="s">
         <v>13</v>
-      </c>
-      <c r="B78" s="79"/>
-      <c r="C78" s="79"/>
-      <c r="D78" s="104"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="3"/>
-      <c r="H78" s="61"/>
-    </row>
-    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="120" t="s">
-        <v>14</v>
-      </c>
-      <c r="B79" s="79" t="s">
-        <v>136</v>
-      </c>
-      <c r="C79" s="79"/>
-      <c r="D79" s="207">
-        <v>285700</v>
-      </c>
-      <c r="E79" s="60">
-        <f>D79*91.91%</f>
-        <v>262586.87</v>
-      </c>
-      <c r="F79" s="49">
-        <f>D79*8.09%</f>
-        <v>23113.13</v>
-      </c>
-      <c r="G79" t="s">
-        <v>112</v>
-      </c>
-      <c r="H79" s="61"/>
-    </row>
-    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="120" t="s">
-        <v>14</v>
-      </c>
-      <c r="B80" s="79" t="s">
-        <v>128</v>
-      </c>
-      <c r="C80" s="79"/>
-      <c r="D80" s="207">
-        <v>112000</v>
-      </c>
-      <c r="E80" s="60">
-        <f>D80*91.91%</f>
-        <v>102939.2</v>
-      </c>
-      <c r="F80" s="49">
-        <f>D80*8.09%</f>
-        <v>9060.7999999999993</v>
-      </c>
-      <c r="H80" s="61"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="120" t="s">
-        <v>80</v>
       </c>
       <c r="B81" s="79"/>
       <c r="C81" s="79"/>
-      <c r="D81" s="207">
-        <v>45000</v>
-      </c>
-      <c r="E81" s="60">
-        <f>D81*91.91%</f>
-        <v>41359.499999999993</v>
-      </c>
-      <c r="F81" s="49">
-        <f>D81*8.09%</f>
-        <v>3640.5</v>
-      </c>
+      <c r="D81" s="104"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="3"/>
       <c r="H81" s="61"/>
-      <c r="J81" s="37"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="120"/>
-      <c r="B82" s="79"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="119" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="79" t="s">
+        <v>127</v>
+      </c>
       <c r="C82" s="79"/>
-      <c r="D82" s="104"/>
+      <c r="D82" s="155">
+        <v>285700</v>
+      </c>
       <c r="E82" s="60">
         <f>D82*91.91%</f>
-        <v>0</v>
+        <v>262586.87</v>
       </c>
       <c r="F82" s="49">
         <f>D82*8.09%</f>
-        <v>0</v>
+        <v>23113.13</v>
+      </c>
+      <c r="G82" t="s">
+        <v>112</v>
       </c>
       <c r="H82" s="61"/>
-      <c r="J82" s="34"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="119"/>
-      <c r="B83" s="119"/>
-      <c r="C83" s="119"/>
-      <c r="D83" s="33">
-        <f>SUM(D79:D82)</f>
-        <v>442700</v>
-      </c>
-      <c r="E83" s="33">
-        <f>SUM(E79:E82)</f>
-        <v>406885.57</v>
-      </c>
-      <c r="F83" s="33">
-        <f>SUM(F79:F82)</f>
-        <v>35814.43</v>
-      </c>
-      <c r="G83" s="34">
-        <f>E83+F83</f>
-        <v>442700</v>
-      </c>
-      <c r="H83" s="61" t="str">
-        <f>IF(D83=G83, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J83" s="34"/>
-    </row>
-    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="120" t="s">
-        <v>73</v>
-      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="119" t="s">
+        <v>80</v>
+      </c>
+      <c r="B83" s="79"/>
+      <c r="C83" s="79"/>
+      <c r="D83" s="155">
+        <v>45000</v>
+      </c>
+      <c r="E83" s="60">
+        <f>D83*91.91%</f>
+        <v>41359.499999999993</v>
+      </c>
+      <c r="F83" s="49">
+        <f>D83*8.09%</f>
+        <v>3640.5</v>
+      </c>
+      <c r="H83" s="61"/>
+      <c r="J83" s="37"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="119"/>
       <c r="B84" s="79"/>
       <c r="C84" s="79"/>
-      <c r="D84" s="37"/>
-      <c r="E84" s="40"/>
-      <c r="F84" s="3"/>
+      <c r="D84" s="104"/>
+      <c r="E84" s="60">
+        <f>D84*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F84" s="49">
+        <f>D84*8.09%</f>
+        <v>0</v>
+      </c>
       <c r="H84" s="61"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="120" t="s">
+      <c r="J84" s="34"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="118"/>
+      <c r="B85" s="118"/>
+      <c r="C85" s="118"/>
+      <c r="D85" s="33">
+        <f>SUM(D82:D84)</f>
+        <v>330700</v>
+      </c>
+      <c r="E85" s="33">
+        <f>SUM(E82:E84)</f>
+        <v>303946.37</v>
+      </c>
+      <c r="F85" s="33">
+        <f>SUM(F82:F84)</f>
+        <v>26753.63</v>
+      </c>
+      <c r="G85" s="34">
+        <f>E85+F85</f>
+        <v>330700</v>
+      </c>
+      <c r="H85" s="61" t="str">
+        <f>IF(D85=G85, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J85" s="34"/>
+    </row>
+    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="B86" s="79"/>
+      <c r="C86" s="79"/>
+      <c r="D86" s="37"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="3"/>
+      <c r="H86" s="61"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="119" t="s">
         <v>74</v>
       </c>
-      <c r="B85" s="79"/>
-      <c r="C85" s="79"/>
-      <c r="D85" s="37">
+      <c r="B87" s="79"/>
+      <c r="C87" s="79"/>
+      <c r="D87" s="158">
         <v>114365.79</v>
       </c>
-      <c r="E85" s="60">
-        <f>D85*91.91%</f>
+      <c r="E87" s="60">
+        <f>D87*91.91%</f>
         <v>105113.59758899998</v>
       </c>
-      <c r="F85" s="49">
-        <f>D85*8.09%</f>
+      <c r="F87" s="49">
+        <f>D87*8.09%</f>
         <v>9252.192411</v>
       </c>
-      <c r="H85" s="61"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="120" t="s">
+      <c r="H87" s="61"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="119" t="s">
         <v>75</v>
       </c>
-      <c r="B86" s="79"/>
-      <c r="C86" s="131"/>
-      <c r="D86" s="37">
+      <c r="B88" s="79"/>
+      <c r="C88" s="130"/>
+      <c r="D88" s="158">
         <v>57500</v>
       </c>
-      <c r="E86" s="60">
-        <f>D86*91.91%</f>
+      <c r="E88" s="60">
+        <f>D88*91.91%</f>
         <v>52848.249999999993</v>
       </c>
-      <c r="F86" s="49">
-        <f>D86*8.09%</f>
+      <c r="F88" s="49">
+        <f>D88*8.09%</f>
         <v>4651.75</v>
       </c>
-      <c r="H86" s="61"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="119" t="s">
+      <c r="H88" s="61"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="B87" s="119"/>
-      <c r="C87" s="119"/>
-      <c r="D87" s="64">
-        <f>SUM(D85:D86)</f>
+      <c r="B89" s="118"/>
+      <c r="C89" s="118"/>
+      <c r="D89" s="64">
+        <f>SUM(D87:D88)</f>
         <v>171865.78999999998</v>
       </c>
-      <c r="E87" s="58">
-        <f t="shared" ref="E87:F87" si="21">SUM(E85:E86)</f>
+      <c r="E89" s="58">
+        <f t="shared" ref="E89:F89" si="22">SUM(E87:E88)</f>
         <v>157961.84758899998</v>
       </c>
-      <c r="F87" s="58">
-        <f t="shared" si="21"/>
+      <c r="F89" s="58">
+        <f t="shared" si="22"/>
         <v>13903.942411</v>
-      </c>
-      <c r="G87" s="34">
-        <f>E87+F87</f>
-        <v>171865.78999999998</v>
-      </c>
-      <c r="H87" s="61" t="str">
-        <f>IF(D87=G87, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="79"/>
-      <c r="B88" s="79"/>
-      <c r="C88" s="79"/>
-      <c r="D88" s="79"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="3"/>
-      <c r="H88" s="61"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="132" t="s">
-        <v>102</v>
-      </c>
-      <c r="B89" s="132"/>
-      <c r="C89" s="146"/>
-      <c r="D89" s="147"/>
-      <c r="E89" s="145">
-        <f>D89*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F89" s="51">
-        <f>D89*8.09%</f>
-        <v>0</v>
       </c>
       <c r="G89" s="34">
         <f>E89+F89</f>
-        <v>0</v>
+        <v>171865.78999999998</v>
       </c>
       <c r="H89" s="61" t="str">
         <f>IF(D89=G89, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="133"/>
-      <c r="B90" s="78"/>
-      <c r="C90" s="78"/>
-      <c r="D90" s="148"/>
-      <c r="E90" s="149"/>
-      <c r="F90" s="149"/>
-      <c r="G90" s="63"/>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="79"/>
+      <c r="B90" s="79"/>
+      <c r="C90" s="79"/>
+      <c r="D90" s="79"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="3"/>
       <c r="H90" s="61"/>
     </row>
-    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="134" t="s">
-        <v>76</v>
-      </c>
-      <c r="B91" s="135"/>
-      <c r="C91" s="136"/>
-      <c r="D91" s="80">
-        <f>SUM(D89+D87+D83+D75+D69+D47+D32+D27+D42)</f>
-        <v>6338472.6799999997</v>
-      </c>
-      <c r="E91" s="59">
-        <f>SUM(E89+E87+E83+E75+E69+E47+E32+E27+E42)</f>
-        <v>5968153.7648879997</v>
-      </c>
-      <c r="F91" s="150">
-        <f>SUM(F27+F42+F47+F69+F75+F83+F87+F89)</f>
-        <v>370318.91511200002</v>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="131" t="s">
+        <v>102</v>
+      </c>
+      <c r="B91" s="131"/>
+      <c r="C91" s="145"/>
+      <c r="D91" s="146"/>
+      <c r="E91" s="144">
+        <f>D91*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F91" s="51">
+        <f>D91*8.09%</f>
+        <v>0</v>
       </c>
       <c r="G91" s="34">
         <f>E91+F91</f>
-        <v>6338472.6799999997</v>
+        <v>0</v>
       </c>
       <c r="H91" s="61" t="str">
         <f>IF(D91=G91, "", "Error")</f>
         <v/>
       </c>
-      <c r="I91" s="76">
-        <f>D91-G91</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="78"/>
+    </row>
+    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="132"/>
       <c r="B92" s="78"/>
       <c r="C92" s="78"/>
-      <c r="D92" s="78"/>
-      <c r="E92" s="34"/>
-    </row>
-    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="137" t="s">
+      <c r="D92" s="147"/>
+      <c r="E92" s="148"/>
+      <c r="F92" s="148"/>
+      <c r="G92" s="63"/>
+      <c r="H92" s="61"/>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="133" t="s">
+        <v>76</v>
+      </c>
+      <c r="B93" s="134"/>
+      <c r="C93" s="135"/>
+      <c r="D93" s="80">
+        <f>SUM(D91+D89+D85+D78+D71+D47+D32+D27+D42)</f>
+        <v>6963780.1600000001</v>
+      </c>
+      <c r="E93" s="59">
+        <f>SUM(E91+E89+E85+E78+E71+E47+E32+E27+E42)</f>
+        <v>6561837.8005559994</v>
+      </c>
+      <c r="F93" s="149">
+        <f>SUM(F27+F42+F47+F71+F78+F85+F89+F91)</f>
+        <v>401942.359444</v>
+      </c>
+      <c r="G93" s="34">
+        <f>E93+F93</f>
+        <v>6963780.1599999992</v>
+      </c>
+      <c r="H93" s="61" t="str">
+        <f>IF(D93=G93, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I93" s="76">
+        <f>D93-G93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="78"/>
+      <c r="B94" s="78"/>
+      <c r="C94" s="78"/>
+      <c r="D94" s="78"/>
+      <c r="E94" s="34"/>
+    </row>
+    <row r="95" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="136" t="s">
         <v>108</v>
       </c>
-      <c r="B93" s="138"/>
-      <c r="C93" s="138"/>
-      <c r="D93" s="78"/>
-      <c r="E93" s="34"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" s="1"/>
-      <c r="C94" s="54"/>
-      <c r="E94" s="34"/>
-    </row>
-    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="1"/>
-      <c r="C95" s="54"/>
+      <c r="B95" s="137"/>
+      <c r="C95" s="137"/>
+      <c r="D95" s="78"/>
       <c r="E95" s="34"/>
     </row>
-    <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="56" t="s">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="C96" s="54"/>
+      <c r="E96" s="34"/>
+    </row>
+    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1"/>
+      <c r="C97" s="54"/>
+      <c r="E97" s="34"/>
+    </row>
+    <row r="98" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="B96" s="57"/>
-      <c r="C96" s="55">
-        <f>SUM(C94:C95)</f>
-        <v>0</v>
-      </c>
-      <c r="E96" s="34"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E97" s="34"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E98" s="52"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A99" s="172" t="s">
+      <c r="B98" s="57"/>
+      <c r="C98" s="55">
+        <f>SUM(C96:C97)</f>
+        <v>0</v>
+      </c>
+      <c r="E98" s="34"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E99" s="34"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E100" s="52"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="180" t="s">
         <v>85</v>
       </c>
-      <c r="B99" s="173"/>
-      <c r="C99" s="173"/>
-      <c r="D99" s="173"/>
-      <c r="E99" s="73" t="s">
+      <c r="B101" s="181"/>
+      <c r="C101" s="181"/>
+      <c r="D101" s="181"/>
+      <c r="E101" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="F99" s="74" t="s">
+      <c r="F101" s="74" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A100" s="169" t="s">
-        <v>122</v>
-      </c>
-      <c r="B100" s="170"/>
-      <c r="C100" s="171"/>
-      <c r="D100" s="37">
-        <v>512600</v>
-      </c>
-      <c r="E100" s="60">
-        <f t="shared" ref="E100:E101" si="22">D100*91.91%</f>
-        <v>471130.66</v>
-      </c>
-      <c r="F100" s="49">
-        <f t="shared" ref="F100:F101" si="23">D100*8.09%</f>
-        <v>41469.339999999997</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="174" t="s">
-        <v>127</v>
-      </c>
-      <c r="B101" s="175"/>
-      <c r="C101" s="176"/>
-      <c r="D101" s="37">
-        <v>300000</v>
-      </c>
-      <c r="E101" s="60">
-        <f t="shared" si="22"/>
-        <v>275730</v>
-      </c>
-      <c r="F101" s="49">
+    <row r="102" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A102" s="177"/>
+      <c r="B102" s="178"/>
+      <c r="C102" s="179"/>
+      <c r="D102" s="37"/>
+      <c r="E102" s="60">
+        <f t="shared" ref="E102:E103" si="23">D102*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F102" s="49">
+        <f t="shared" ref="F102:F103" si="24">D102*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="182"/>
+      <c r="B103" s="183"/>
+      <c r="C103" s="184"/>
+      <c r="D103" s="37"/>
+      <c r="E103" s="60">
         <f t="shared" si="23"/>
-        <v>24270</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="166" t="s">
+        <v>0</v>
+      </c>
+      <c r="F103" s="49">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="174" t="s">
         <v>25</v>
       </c>
-      <c r="B102" s="167"/>
-      <c r="C102" s="168"/>
-      <c r="D102" s="72">
-        <f>SUM(D100:D101)</f>
-        <v>812600</v>
-      </c>
-      <c r="E102" s="72">
-        <f>SUM(E100:E101)</f>
-        <v>746860.65999999992</v>
-      </c>
-      <c r="F102" s="72">
-        <f>SUM(F100:F101)</f>
-        <v>65739.34</v>
-      </c>
-      <c r="H102" s="34">
-        <f>E102+F102</f>
-        <v>812599.99999999988</v>
-      </c>
-      <c r="I102" s="61" t="str">
-        <f>IF(D102=H102, "", "Error")</f>
+      <c r="B104" s="175"/>
+      <c r="C104" s="176"/>
+      <c r="D104" s="72">
+        <f>SUM(D102:D103)</f>
+        <v>0</v>
+      </c>
+      <c r="E104" s="72">
+        <f>SUM(E102:E103)</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="72">
+        <f>SUM(F102:F103)</f>
+        <v>0</v>
+      </c>
+      <c r="H104" s="34">
+        <f>E104+F104</f>
+        <v>0</v>
+      </c>
+      <c r="I104" s="61" t="str">
+        <f>IF(D104=H104, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E104" s="34"/>
-    </row>
-    <row r="105" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="28" t="s">
+    <row r="106" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E106" s="34"/>
+    </row>
+    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="B105" s="29">
-        <f>D91</f>
-        <v>6338472.6799999997</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="30" t="s">
+      <c r="B107" s="29">
+        <f>D93</f>
+        <v>6963780.1600000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B106" s="31">
-        <f>D91-D89</f>
-        <v>6338472.6799999997</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D107" s="156"/>
-      <c r="E107" s="156"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="9" t="s">
+      <c r="B108" s="31">
+        <f>D93-D91</f>
+        <v>6963780.1600000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D109" s="164"/>
+      <c r="E109" s="164"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B108" s="10"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="156"/>
-      <c r="E108" s="156"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="12" t="s">
+      <c r="B110" s="10"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="164"/>
+      <c r="E110" s="164"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B109" s="5">
-        <v>10470066.57147561</v>
-      </c>
-      <c r="C109" s="13"/>
-      <c r="D109" s="156"/>
-      <c r="E109" s="156"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="14" t="s">
+      <c r="B111" s="5">
+        <v>12981485.379368611</v>
+      </c>
+      <c r="C111" s="13"/>
+      <c r="D111" s="164"/>
+      <c r="E111" s="164"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B110" s="23">
+      <c r="B112" s="23">
         <f>PRORRATEO!G52</f>
-        <v>8886432.0578930005</v>
-      </c>
-      <c r="C110" s="13" t="s">
+        <v>7986260.3999579996</v>
+      </c>
+      <c r="C112" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D110" s="156"/>
-      <c r="E110" s="156"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="14" t="s">
+      <c r="D112" s="164"/>
+      <c r="E112" s="164"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B111" s="75">
-        <f>-B106</f>
-        <v>-6338472.6799999997</v>
-      </c>
-      <c r="C111" s="11"/>
-      <c r="D111" s="156"/>
-      <c r="E111" s="156"/>
-      <c r="G111" s="37"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="14" t="s">
+      <c r="B113" s="75">
+        <f>-B108</f>
+        <v>-6963780.1600000001</v>
+      </c>
+      <c r="C113" s="11"/>
+      <c r="D113" s="164"/>
+      <c r="E113" s="164"/>
+      <c r="G113" s="37"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B112" s="75">
-        <f>-D102</f>
-        <v>-812600</v>
-      </c>
-      <c r="C112" s="11"/>
-      <c r="D112" s="156"/>
-      <c r="E112" s="156"/>
-      <c r="G112" s="43"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A113" s="14" t="s">
+      <c r="B114" s="75">
+        <f>-D104</f>
+        <v>0</v>
+      </c>
+      <c r="C114" s="11"/>
+      <c r="D114" s="164"/>
+      <c r="E114" s="164"/>
+      <c r="G114" s="43"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B113" s="75">
-        <f>-B119</f>
+      <c r="B115" s="75">
+        <f>-B121</f>
         <v>-20000</v>
       </c>
-      <c r="C113" s="15"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A114" s="14" t="s">
+      <c r="C115" s="15"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B114" s="24">
-        <f>-C96</f>
-        <v>0</v>
-      </c>
-      <c r="C114" s="15"/>
-      <c r="E114" s="34"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A115" s="12" t="s">
+      <c r="B116" s="24">
+        <f>-C98</f>
+        <v>0</v>
+      </c>
+      <c r="C116" s="15"/>
+      <c r="E116" s="34"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B115" s="16">
-        <f>SUM(B109:B114)</f>
-        <v>12185425.949368611</v>
-      </c>
-      <c r="C115" s="62"/>
-      <c r="D115" s="34"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A116" s="15"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="18"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C117" s="11"/>
+      <c r="B117" s="16">
+        <f>SUM(B111:B116)</f>
+        <v>13983965.61932661</v>
+      </c>
+      <c r="C117" s="62"/>
       <c r="D117" s="34"/>
-      <c r="E117" s="76"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A118" s="9" t="s">
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" s="15"/>
+      <c r="C118" s="11"/>
+      <c r="D118" s="18"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C119" s="11"/>
+      <c r="D119" s="34"/>
+      <c r="E119" s="76"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B118" s="86">
+      <c r="B120" s="86">
         <v>-102694.54000000004</v>
       </c>
-      <c r="C118" s="17"/>
-      <c r="D118" s="76"/>
-      <c r="E118" s="76"/>
-      <c r="F118" s="76"/>
-    </row>
-    <row r="119" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B119" s="24">
+      <c r="C120" s="17"/>
+      <c r="D120" s="76"/>
+      <c r="E120" s="76"/>
+      <c r="F120" s="76"/>
+    </row>
+    <row r="121" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" s="24">
         <v>20000</v>
       </c>
-      <c r="C119" s="17"/>
-      <c r="D119" s="76"/>
-      <c r="E119" s="81"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A120" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B120" s="75">
-        <v>-20000</v>
-      </c>
-      <c r="C120" s="17"/>
-      <c r="E120" s="34"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A121" s="12"/>
-      <c r="B121" s="75"/>
       <c r="C121" s="17"/>
-      <c r="D121" s="139"/>
-      <c r="E121" s="34"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A122" s="26" t="s">
+      <c r="D121" s="76"/>
+      <c r="E121" s="81"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122" s="12"/>
+      <c r="B122" s="75"/>
+      <c r="C122" s="17"/>
+      <c r="E122" s="34"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123" s="12"/>
+      <c r="B123" s="75"/>
+      <c r="C123" s="17"/>
+      <c r="D123" s="138"/>
+      <c r="E123" s="34"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B122" s="27">
-        <f>SUM(B118:B121)</f>
-        <v>-102694.54000000004</v>
-      </c>
-      <c r="C122" s="17"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C123" s="18"/>
-      <c r="D123" s="76"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B124" s="15"/>
-      <c r="C124" s="11"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N126" s="6"/>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B129" s="155"/>
-      <c r="C129" s="155"/>
-      <c r="D129" s="155"/>
-      <c r="E129" s="155"/>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B130" s="155"/>
-      <c r="C130" s="155"/>
-      <c r="D130" s="155"/>
-      <c r="E130" s="155"/>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B131" s="155"/>
-      <c r="C131" s="155"/>
-      <c r="D131" s="155"/>
-      <c r="E131" s="155"/>
-    </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B132" s="155"/>
-      <c r="C132" s="155"/>
-      <c r="D132" s="155"/>
-      <c r="E132" s="155"/>
-    </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B133" s="155"/>
-      <c r="C133" s="155"/>
-      <c r="D133" s="155"/>
-      <c r="E133" s="155"/>
+      <c r="B124" s="27">
+        <f>SUM(B120:B123)</f>
+        <v>-82694.540000000037</v>
+      </c>
+      <c r="C124" s="17"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C125" s="18"/>
+      <c r="D125" s="76"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B126" s="15"/>
+      <c r="C126" s="11"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N128" s="6"/>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B131" s="163"/>
+      <c r="C131" s="163"/>
+      <c r="D131" s="163"/>
+      <c r="E131" s="163"/>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B132" s="163"/>
+      <c r="C132" s="163"/>
+      <c r="D132" s="163"/>
+      <c r="E132" s="163"/>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B133" s="163"/>
+      <c r="C133" s="163"/>
+      <c r="D133" s="163"/>
+      <c r="E133" s="163"/>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B134" s="163"/>
+      <c r="C134" s="163"/>
+      <c r="D134" s="163"/>
+      <c r="E134" s="163"/>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B135" s="163"/>
+      <c r="C135" s="163"/>
+      <c r="D135" s="163"/>
+      <c r="E135" s="163"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B129:E133"/>
-    <mergeCell ref="D107:E112"/>
+    <mergeCell ref="B131:E135"/>
+    <mergeCell ref="D109:E114"/>
     <mergeCell ref="B14:D17"/>
+    <mergeCell ref="A104:C104"/>
     <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A67:C67"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A68:C68"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3792,65 +3876,65 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
-    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="195" t="str">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="203" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 18/06</v>
       </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="197"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="205"/>
       <c r="K1" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="186">
-        <f>RESUMEN!D91</f>
-        <v>6338472.6799999997</v>
-      </c>
-      <c r="M1" s="187"/>
+      <c r="L1" s="192">
+        <f>RESUMEN!D93</f>
+        <v>6963780.1600000001</v>
+      </c>
+      <c r="M1" s="193"/>
       <c r="N1" s="91"/>
       <c r="O1" s="50">
         <f>L1*8.09%</f>
-        <v>512782.43981199997</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="198"/>
-      <c r="B2" s="199"/>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199"/>
-      <c r="E2" s="199"/>
-      <c r="F2" s="199"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="199"/>
-      <c r="J2" s="200"/>
+        <v>563369.81494399998</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="206"/>
+      <c r="B2" s="207"/>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="207"/>
+      <c r="H2" s="207"/>
+      <c r="I2" s="207"/>
+      <c r="J2" s="208"/>
       <c r="K2" s="92" t="s">
         <v>95</v>
       </c>
@@ -3862,116 +3946,116 @@
       <c r="N2" s="94"/>
       <c r="O2" s="50">
         <f>O1-K7-553-50-86-8</f>
-        <v>201662.21985399997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="198"/>
-      <c r="B3" s="199"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="199"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="199"/>
-      <c r="I3" s="199"/>
-      <c r="J3" s="200"/>
+        <v>252249.59498599998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="206"/>
+      <c r="B3" s="207"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="207"/>
+      <c r="I3" s="207"/>
+      <c r="J3" s="208"/>
       <c r="K3" s="92" t="s">
         <v>100</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="95">
-        <f>RESUMEN!D102</f>
-        <v>812600</v>
+        <f>RESUMEN!D104</f>
+        <v>0</v>
       </c>
       <c r="N3" s="96"/>
       <c r="O3" s="8"/>
     </row>
-    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="201"/>
-      <c r="B4" s="202"/>
-      <c r="C4" s="202"/>
-      <c r="D4" s="202"/>
-      <c r="E4" s="202"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="202"/>
-      <c r="H4" s="202"/>
-      <c r="I4" s="202"/>
-      <c r="J4" s="203"/>
+    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="209"/>
+      <c r="B4" s="210"/>
+      <c r="C4" s="210"/>
+      <c r="D4" s="210"/>
+      <c r="E4" s="210"/>
+      <c r="F4" s="210"/>
+      <c r="G4" s="210"/>
+      <c r="H4" s="210"/>
+      <c r="I4" s="210"/>
+      <c r="J4" s="211"/>
       <c r="K4" s="97" t="s">
         <v>95</v>
       </c>
       <c r="L4" s="98"/>
       <c r="M4" s="99">
-        <v>812600</v>
+        <v>0</v>
       </c>
       <c r="N4" s="100"/>
       <c r="O4" s="50">
         <f>M3/3</f>
-        <v>270866.66666666669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="183" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="204" t="s">
+      <c r="B5" s="212" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="183" t="s">
+      <c r="C5" s="196" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="193" t="s">
+      <c r="D5" s="201" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="183" t="s">
+      <c r="E5" s="196" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="183" t="s">
+      <c r="F5" s="196" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="183" t="s">
+      <c r="G5" s="196" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="190" t="s">
+      <c r="H5" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="193" t="s">
+      <c r="I5" s="201" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="188" t="s">
+      <c r="J5" s="194" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="188" t="s">
+      <c r="K5" s="194" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="188" t="s">
+      <c r="L5" s="194" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="188" t="s">
+      <c r="M5" s="194" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="188" t="s">
+      <c r="N5" s="194" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="184"/>
-      <c r="B6" s="205"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="184"/>
-      <c r="H6" s="191"/>
-      <c r="I6" s="194"/>
-      <c r="J6" s="192"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="192"/>
-      <c r="M6" s="189"/>
-      <c r="N6" s="189"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="197"/>
+      <c r="B6" s="213"/>
+      <c r="C6" s="197"/>
+      <c r="D6" s="214"/>
+      <c r="E6" s="197"/>
+      <c r="F6" s="197"/>
+      <c r="G6" s="197"/>
+      <c r="H6" s="199"/>
+      <c r="I6" s="202"/>
+      <c r="J6" s="200"/>
+      <c r="K6" s="195"/>
+      <c r="L6" s="200"/>
+      <c r="M6" s="195"/>
+      <c r="N6" s="195"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -3986,21 +4070,21 @@
         <v>8.09</v>
       </c>
       <c r="F7" s="19">
-        <v>462245.18789300008</v>
-      </c>
-      <c r="G7" s="105">
+        <v>376162.55995799997</v>
+      </c>
+      <c r="G7" s="159">
         <f>F7</f>
-        <v>462245.18789300008</v>
+        <v>376162.55995799997</v>
       </c>
       <c r="H7" s="46">
         <f>F7-G7</f>
         <v>0</v>
       </c>
       <c r="I7" s="32">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J7" s="19">
-        <v>65739.34</v>
+        <v>0</v>
       </c>
       <c r="K7" s="19">
         <v>310423.219958</v>
@@ -4008,14 +4092,14 @@
       <c r="L7" s="25"/>
       <c r="M7" s="2">
         <f>K7+J7+H7+L7</f>
-        <v>376162.55995799997</v>
+        <v>310423.219958</v>
       </c>
       <c r="N7" s="5">
         <f>M7*6% + M7</f>
-        <v>398732.31355547998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>329048.61315548001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
@@ -4030,21 +4114,21 @@
         <v>2.21</v>
       </c>
       <c r="F8" s="19">
-        <v>187822.93683118254</v>
-      </c>
-      <c r="G8" s="105">
-        <v>188000</v>
+        <v>187672.93683118254</v>
+      </c>
+      <c r="G8" s="159">
+        <v>190000</v>
       </c>
       <c r="H8" s="46">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>-177.0631688174617</v>
+        <v>-2327.0631688174617</v>
       </c>
       <c r="I8" s="32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J8" s="19">
         <f>M$4*E8%</f>
-        <v>17958.46</v>
+        <v>0</v>
       </c>
       <c r="K8" s="19">
         <f>M$2*E8 /100</f>
@@ -4053,14 +4137,14 @@
       <c r="L8" s="88"/>
       <c r="M8" s="2">
         <f>K8+J8+H8+L8</f>
-        <v>187672.93683118254</v>
+        <v>167564.47683118255</v>
       </c>
       <c r="N8" s="5">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>198933.31304105348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>177618.34544105351</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
@@ -4077,7 +4161,7 @@
       <c r="F9" s="19">
         <v>357849.60286759672</v>
       </c>
-      <c r="G9" s="106">
+      <c r="G9" s="160">
         <f>403750-G34</f>
         <v>357850</v>
       </c>
@@ -4086,11 +4170,11 @@
         <v>-0.39713240327546373</v>
       </c>
       <c r="I9" s="32">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J9" s="19">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
-        <v>34210.46</v>
+        <v>0</v>
       </c>
       <c r="K9" s="19">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
@@ -4099,14 +4183,14 @@
       <c r="L9" s="88"/>
       <c r="M9" s="2">
         <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>357849.60286759672</v>
+        <v>323639.1428675967</v>
       </c>
       <c r="N9" s="5">
         <f t="shared" si="1"/>
-        <v>379320.57903965254</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>343057.49143965251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -4121,21 +4205,21 @@
         <v>2.84</v>
       </c>
       <c r="F10" s="19">
-        <v>241400</v>
-      </c>
-      <c r="G10" s="105">
-        <v>241000</v>
+        <v>241800</v>
+      </c>
+      <c r="G10" s="159">
+        <v>218000</v>
       </c>
       <c r="H10" s="46">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>23800</v>
       </c>
       <c r="I10" s="32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J10" s="19">
         <f t="shared" si="2"/>
-        <v>23077.84</v>
+        <v>0</v>
       </c>
       <c r="K10" s="19">
         <f t="shared" si="3"/>
@@ -4144,14 +4228,14 @@
       <c r="L10" s="88"/>
       <c r="M10" s="2">
         <f t="shared" si="4"/>
-        <v>241800</v>
+        <v>242122.16</v>
       </c>
       <c r="N10" s="5">
         <f t="shared" si="1"/>
-        <v>256308</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>256649.4896</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>31</v>
       </c>
@@ -4168,7 +4252,7 @@
       <c r="F11" s="19">
         <v>291550</v>
       </c>
-      <c r="G11" s="105">
+      <c r="G11" s="159">
         <f>F11</f>
         <v>291550</v>
       </c>
@@ -4177,11 +4261,11 @@
         <v>0</v>
       </c>
       <c r="I11" s="32">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J11" s="19">
         <f t="shared" si="2"/>
-        <v>27872.180000000004</v>
+        <v>0</v>
       </c>
       <c r="K11" s="19">
         <f t="shared" si="3"/>
@@ -4190,15 +4274,15 @@
       <c r="L11" s="88"/>
       <c r="M11" s="2">
         <f t="shared" si="4"/>
-        <v>291550</v>
+        <v>263677.82</v>
       </c>
       <c r="N11" s="5">
         <f t="shared" si="1"/>
-        <v>309043</v>
+        <v>279498.48920000001</v>
       </c>
       <c r="P11" s="34"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>34</v>
       </c>
@@ -4215,7 +4299,7 @@
       <c r="F12" s="19">
         <v>241400</v>
       </c>
-      <c r="G12" s="106">
+      <c r="G12" s="160">
         <f>F12</f>
         <v>241400</v>
       </c>
@@ -4224,11 +4308,11 @@
         <v>0</v>
       </c>
       <c r="I12" s="32">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J12" s="19">
         <f t="shared" si="2"/>
-        <v>23077.84</v>
+        <v>0</v>
       </c>
       <c r="K12" s="19">
         <f t="shared" si="3"/>
@@ -4237,14 +4321,14 @@
       <c r="L12" s="88"/>
       <c r="M12" s="2">
         <f t="shared" si="4"/>
-        <v>241400</v>
+        <v>218322.16</v>
       </c>
       <c r="N12" s="5">
         <f t="shared" si="1"/>
-        <v>255884</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>231421.4896</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>34</v>
       </c>
@@ -4261,20 +4345,20 @@
       <c r="F13" s="19">
         <v>291550.81741924176</v>
       </c>
-      <c r="G13" s="106">
-        <f>341700-G50</f>
-        <v>291550</v>
+      <c r="G13" s="160">
+        <f>341701-G50</f>
+        <v>291551</v>
       </c>
       <c r="H13" s="46">
         <f t="shared" si="0"/>
-        <v>0.81741924176458269</v>
+        <v>-0.18258075823541731</v>
       </c>
       <c r="I13" s="32">
         <v>6</v>
       </c>
       <c r="J13" s="19">
         <f t="shared" si="2"/>
-        <v>27872.180000000004</v>
+        <v>0</v>
       </c>
       <c r="K13" s="19">
         <f t="shared" si="3"/>
@@ -4283,14 +4367,14 @@
       <c r="L13" s="88"/>
       <c r="M13" s="2">
         <f t="shared" si="4"/>
-        <v>291550.81741924176</v>
+        <v>263677.63741924177</v>
       </c>
       <c r="N13" s="5">
         <f t="shared" si="1"/>
-        <v>309043.86646439624</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>279498.29566439625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>36</v>
       </c>
@@ -4305,21 +4389,21 @@
         <v>2.84</v>
       </c>
       <c r="F14" s="19">
-        <v>523768.96666666662</v>
-      </c>
-      <c r="G14" s="105">
-        <v>241400</v>
+        <v>555195.10466666659</v>
+      </c>
+      <c r="G14" s="159">
+        <v>218322</v>
       </c>
       <c r="H14" s="46">
         <f t="shared" si="0"/>
-        <v>282368.96666666662</v>
+        <v>336873.10466666659</v>
       </c>
       <c r="I14" s="32">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J14" s="19">
         <f t="shared" si="2"/>
-        <v>23077.84</v>
+        <v>0</v>
       </c>
       <c r="K14" s="19">
         <f t="shared" si="3"/>
@@ -4328,14 +4412,14 @@
       <c r="L14" s="88"/>
       <c r="M14" s="2">
         <f t="shared" si="4"/>
-        <v>523768.96666666662</v>
+        <v>555195.26466666663</v>
       </c>
       <c r="N14" s="5">
         <f t="shared" si="1"/>
-        <v>555195.10466666659</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>588506.98054666666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>36</v>
       </c>
@@ -4350,22 +4434,19 @@
         <v>3.43</v>
       </c>
       <c r="F15" s="19">
-        <v>358517.06325632613</v>
-      </c>
-      <c r="G15" s="106">
-        <f>401017-G35</f>
-        <v>358517</v>
-      </c>
+        <v>291550.06325632613</v>
+      </c>
+      <c r="G15" s="105"/>
       <c r="H15" s="46">
         <f t="shared" si="0"/>
-        <v>6.3256326131522655E-2</v>
+        <v>291550.06325632613</v>
       </c>
       <c r="I15" s="32">
         <v>9</v>
       </c>
       <c r="J15" s="19">
         <f t="shared" si="2"/>
-        <v>27872.180000000004</v>
+        <v>0</v>
       </c>
       <c r="K15" s="19">
         <f t="shared" si="3"/>
@@ -4374,14 +4455,14 @@
       <c r="L15" s="88"/>
       <c r="M15" s="2">
         <f t="shared" si="4"/>
-        <v>291550.06325632613</v>
+        <v>555227.8832563262</v>
       </c>
       <c r="N15" s="5">
         <f t="shared" si="1"/>
-        <v>309043.06705170567</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>588541.55625170574</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
@@ -4398,7 +4479,7 @@
       <c r="F16" s="19">
         <v>241400.07982700004</v>
       </c>
-      <c r="G16" s="106">
+      <c r="G16" s="160">
         <f>283050-G49</f>
         <v>241400</v>
       </c>
@@ -4407,11 +4488,11 @@
         <v>7.9827000037766993E-2</v>
       </c>
       <c r="I16" s="32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J16" s="19">
         <f t="shared" si="2"/>
-        <v>23077.84</v>
+        <v>0</v>
       </c>
       <c r="K16" s="19">
         <f t="shared" si="3"/>
@@ -4420,14 +4501,14 @@
       <c r="L16" s="88"/>
       <c r="M16" s="2">
         <f t="shared" si="4"/>
-        <v>241400.07982700004</v>
+        <v>218322.23982700004</v>
       </c>
       <c r="N16" s="5">
         <f t="shared" si="1"/>
-        <v>255884.08461662004</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+        <v>231421.57421662004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
@@ -4442,40 +4523,38 @@
         <v>3.43</v>
       </c>
       <c r="F17" s="19">
-        <v>291550.30734444817</v>
-      </c>
-      <c r="G17" s="105">
-        <f>380749-G47-G48</f>
-        <v>296599</v>
+        <v>324891.38578511507</v>
+      </c>
+      <c r="G17" s="159">
+        <f>380749-G47-G48+14951</f>
+        <v>306501</v>
       </c>
       <c r="H17" s="46">
         <f t="shared" si="0"/>
-        <v>-5048.6926555518294</v>
+        <v>18390.385785115068</v>
       </c>
       <c r="I17" s="32">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" s="19">
         <f t="shared" si="2"/>
-        <v>27872.180000000004</v>
+        <v>0</v>
       </c>
       <c r="K17" s="19">
         <f t="shared" si="3"/>
         <v>263677.82</v>
       </c>
-      <c r="L17" s="88">
-        <v>20000</v>
-      </c>
+      <c r="L17" s="88"/>
       <c r="M17" s="2">
         <f t="shared" si="4"/>
-        <v>306501.30734444817</v>
+        <v>282068.20578511507</v>
       </c>
       <c r="N17" s="5">
         <f t="shared" si="1"/>
-        <v>324891.38578511507</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>298992.29813222197</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
@@ -4490,11 +4569,11 @@
         <v>2.84</v>
       </c>
       <c r="F18" s="19">
-        <v>241399.50379991793</v>
-      </c>
-      <c r="G18" s="105">
-        <f>289850-G51</f>
-        <v>241400</v>
+        <v>261399.50379991793</v>
+      </c>
+      <c r="G18" s="159">
+        <f>309850-G51</f>
+        <v>261400</v>
       </c>
       <c r="H18" s="46">
         <f t="shared" si="0"/>
@@ -4505,28 +4584,26 @@
       </c>
       <c r="J18" s="19">
         <f t="shared" si="2"/>
-        <v>23077.84</v>
+        <v>0</v>
       </c>
       <c r="K18" s="19">
         <f t="shared" si="3"/>
         <v>218322.16</v>
       </c>
-      <c r="L18" s="88">
-        <v>20000</v>
-      </c>
+      <c r="L18" s="88"/>
       <c r="M18" s="2">
         <f t="shared" si="4"/>
-        <v>261399.50379991793</v>
+        <v>218321.66379991794</v>
       </c>
       <c r="N18" s="5">
         <f t="shared" si="1"/>
-        <v>277083.47402791301</v>
+        <v>231420.96362791301</v>
       </c>
       <c r="P18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
@@ -4541,22 +4618,22 @@
         <v>3.43</v>
       </c>
       <c r="F19" s="19">
-        <v>311549.81964850146</v>
-      </c>
-      <c r="G19" s="106">
-        <f>337450+20000-G41</f>
-        <v>311550</v>
+        <v>291549.81964850146</v>
+      </c>
+      <c r="G19" s="160">
+        <f>309578-G41</f>
+        <v>263678</v>
       </c>
       <c r="H19" s="46">
         <f t="shared" si="0"/>
-        <v>-0.18035149853676558</v>
+        <v>27871.819648501463</v>
       </c>
       <c r="I19" s="32">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J19" s="19">
         <f t="shared" si="2"/>
-        <v>27872.180000000004</v>
+        <v>0</v>
       </c>
       <c r="K19" s="19">
         <f t="shared" si="3"/>
@@ -4565,14 +4642,14 @@
       <c r="L19" s="88"/>
       <c r="M19" s="2">
         <f t="shared" si="4"/>
-        <v>291549.81964850146</v>
+        <v>291549.63964850147</v>
       </c>
       <c r="N19" s="5">
         <f t="shared" si="1"/>
-        <v>309042.80882741156</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>309042.61802741158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
@@ -4589,7 +4666,7 @@
       <c r="F20" s="19">
         <v>241399.65585707471</v>
       </c>
-      <c r="G20" s="105">
+      <c r="G20" s="159">
         <f>283050-G38</f>
         <v>241400</v>
       </c>
@@ -4602,7 +4679,7 @@
       </c>
       <c r="J20" s="19">
         <f t="shared" si="2"/>
-        <v>23077.84</v>
+        <v>0</v>
       </c>
       <c r="K20" s="19">
         <f t="shared" si="3"/>
@@ -4611,14 +4688,14 @@
       <c r="L20" s="88"/>
       <c r="M20" s="2">
         <f t="shared" si="4"/>
-        <v>241399.65585707471</v>
+        <v>218321.81585707472</v>
       </c>
       <c r="N20" s="5">
         <f t="shared" si="1"/>
-        <v>255883.63520849921</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+        <v>231421.12480849921</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>43</v>
       </c>
@@ -4635,7 +4712,7 @@
       <c r="F21" s="19">
         <v>291549.9952936371</v>
       </c>
-      <c r="G21" s="105">
+      <c r="G21" s="159">
         <f>337450-G45</f>
         <v>291550</v>
       </c>
@@ -4648,7 +4725,7 @@
       </c>
       <c r="J21" s="19">
         <f t="shared" si="2"/>
-        <v>27872.180000000004</v>
+        <v>0</v>
       </c>
       <c r="K21" s="19">
         <f t="shared" si="3"/>
@@ -4657,14 +4734,14 @@
       <c r="L21" s="88"/>
       <c r="M21" s="2">
         <f t="shared" si="4"/>
-        <v>291549.9952936371</v>
+        <v>263677.8152936371</v>
       </c>
       <c r="N21" s="5">
         <f t="shared" si="1"/>
-        <v>309042.99501125532</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+        <v>279498.48421125533</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>46</v>
       </c>
@@ -4681,7 +4758,7 @@
       <c r="F22" s="19">
         <v>241400</v>
       </c>
-      <c r="G22" s="105">
+      <c r="G22" s="159">
         <f>F22</f>
         <v>241400</v>
       </c>
@@ -4694,7 +4771,7 @@
       </c>
       <c r="J22" s="19">
         <f t="shared" si="2"/>
-        <v>23077.84</v>
+        <v>0</v>
       </c>
       <c r="K22" s="19">
         <f t="shared" si="3"/>
@@ -4703,14 +4780,14 @@
       <c r="L22" s="88"/>
       <c r="M22" s="2">
         <f t="shared" si="4"/>
-        <v>241400</v>
+        <v>218322.16</v>
       </c>
       <c r="N22" s="5">
         <f t="shared" si="1"/>
-        <v>255884</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+        <v>231421.4896</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>46</v>
       </c>
@@ -4725,22 +4802,22 @@
         <v>3.43</v>
       </c>
       <c r="F23" s="19">
-        <v>309698.66790342226</v>
-      </c>
-      <c r="G23" s="106">
-        <f>353000-G46</f>
-        <v>310500</v>
+        <v>290748.66790342226</v>
+      </c>
+      <c r="G23" s="160">
+        <f>335000-G46</f>
+        <v>292500</v>
       </c>
       <c r="H23" s="46">
         <f t="shared" si="0"/>
-        <v>-801.33209657773841</v>
+        <v>-1751.3320965777384</v>
       </c>
       <c r="I23" s="32">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J23" s="19">
         <f t="shared" si="2"/>
-        <v>27872.180000000004</v>
+        <v>0</v>
       </c>
       <c r="K23" s="19">
         <f t="shared" si="3"/>
@@ -4749,14 +4826,14 @@
       <c r="L23" s="88"/>
       <c r="M23" s="2">
         <f t="shared" si="4"/>
-        <v>290748.66790342226</v>
+        <v>261926.48790342227</v>
       </c>
       <c r="N23" s="5">
         <f t="shared" si="1"/>
-        <v>308193.58797762758</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>277642.07717762759</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>48</v>
       </c>
@@ -4771,22 +4848,22 @@
         <v>2.84</v>
       </c>
       <c r="F24" s="19">
-        <v>235785.37342107471</v>
-      </c>
-      <c r="G24" s="105">
-        <f>278000-G37</f>
-        <v>236350</v>
+        <v>240835.37342107471</v>
+      </c>
+      <c r="G24" s="159">
+        <f>290000-G37</f>
+        <v>248350</v>
       </c>
       <c r="H24" s="46">
         <f t="shared" si="0"/>
-        <v>-564.62657892529387</v>
+        <v>-7514.6265789252939</v>
       </c>
       <c r="I24" s="77">
         <v>7</v>
       </c>
       <c r="J24" s="19">
         <f t="shared" si="2"/>
-        <v>23077.84</v>
+        <v>0</v>
       </c>
       <c r="K24" s="19">
         <f t="shared" si="3"/>
@@ -4795,14 +4872,14 @@
       <c r="L24" s="88"/>
       <c r="M24" s="2">
         <f t="shared" si="4"/>
-        <v>240835.37342107471</v>
+        <v>210807.53342107471</v>
       </c>
       <c r="N24" s="5">
         <f t="shared" si="1"/>
-        <v>255285.49582633917</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>223455.9854263392</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -4817,21 +4894,21 @@
         <v>3.43</v>
       </c>
       <c r="F25" s="19">
-        <v>263321.66666666669</v>
-      </c>
-      <c r="G25" s="106">
-        <v>279120.87</v>
+        <v>275750.79666666669</v>
+      </c>
+      <c r="G25" s="160">
+        <v>292296.84000000003</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="0"/>
-        <v>-15799.203333333309</v>
+        <v>-16546.043333333335</v>
       </c>
       <c r="I25" s="32">
         <v>7</v>
       </c>
       <c r="J25" s="19">
         <f t="shared" si="2"/>
-        <v>27872.180000000004</v>
+        <v>0</v>
       </c>
       <c r="K25" s="19">
         <f t="shared" si="3"/>
@@ -4840,17 +4917,17 @@
       <c r="L25" s="89"/>
       <c r="M25" s="2">
         <f t="shared" si="4"/>
-        <v>275750.79666666669</v>
+        <v>247131.77666666667</v>
       </c>
       <c r="N25" s="5">
         <f t="shared" si="1"/>
-        <v>292295.84446666669</v>
+        <v>261959.68326666666</v>
       </c>
       <c r="P25" s="53"/>
       <c r="Q25" s="53"/>
       <c r="R25" s="53"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>50</v>
       </c>
@@ -4865,22 +4942,22 @@
         <v>6</v>
       </c>
       <c r="F26" s="19">
-        <v>-1088811.3406672962</v>
-      </c>
-      <c r="G26" s="106">
-        <f>900000+900000-G30-G31-G36</f>
-        <v>1664850</v>
+        <v>-2243661.3406672962</v>
+      </c>
+      <c r="G26" s="160">
+        <f>-G30-G31-G36</f>
+        <v>-135150</v>
       </c>
       <c r="H26" s="47">
         <f t="shared" si="0"/>
-        <v>-2753661.3406672962</v>
-      </c>
-      <c r="I26" s="151">
-        <v>4</v>
+        <v>-2108511.3406672962</v>
+      </c>
+      <c r="I26" s="150" t="s">
+        <v>146</v>
       </c>
       <c r="J26" s="19">
         <f t="shared" si="2"/>
-        <v>48756</v>
+        <v>0</v>
       </c>
       <c r="K26" s="19">
         <f t="shared" si="3"/>
@@ -4889,14 +4966,14 @@
       <c r="L26" s="88"/>
       <c r="M26" s="2">
         <f t="shared" si="4"/>
-        <v>-2243661.3406672962</v>
+        <v>-1647267.3406672962</v>
       </c>
       <c r="N26" s="5">
         <f t="shared" si="1"/>
-        <v>-2378281.0211073342</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-1746103.381107334</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
@@ -4913,20 +4990,20 @@
       <c r="F27" s="19">
         <v>500650.37128526531</v>
       </c>
-      <c r="G27" s="105">
-        <f>599250-G39-G40</f>
-        <v>500650</v>
+      <c r="G27" s="159">
+        <f>600000-G39-G40</f>
+        <v>501400</v>
       </c>
       <c r="H27" s="46">
         <f t="shared" si="0"/>
-        <v>0.37128526531159878</v>
+        <v>-749.6287147346884</v>
       </c>
       <c r="I27" s="32">
         <v>13</v>
       </c>
       <c r="J27" s="19">
         <f t="shared" si="2"/>
-        <v>47862.139999999992</v>
+        <v>0</v>
       </c>
       <c r="K27" s="19">
         <f t="shared" si="3"/>
@@ -4935,15 +5012,15 @@
       <c r="L27" s="88"/>
       <c r="M27" s="2">
         <f t="shared" si="4"/>
-        <v>500650.37128526531</v>
+        <v>452038.2312852653</v>
       </c>
       <c r="N27" s="5">
         <f t="shared" si="1"/>
-        <v>530689.39356238127</v>
+        <v>479160.52516238124</v>
       </c>
       <c r="R27" s="53"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>54</v>
       </c>
@@ -4958,22 +5035,22 @@
         <v>5.89</v>
       </c>
       <c r="F28" s="19">
-        <v>500591.17449320736</v>
-      </c>
-      <c r="G28" s="105">
-        <f>592000-G32-G33</f>
-        <v>501900</v>
+        <v>499341.17449320736</v>
+      </c>
+      <c r="G28" s="159">
+        <f>600000-G32-G33</f>
+        <v>509900</v>
       </c>
       <c r="H28" s="46">
         <f t="shared" si="0"/>
-        <v>-1308.8255067926366</v>
+        <v>-10558.825506792637</v>
       </c>
       <c r="I28" s="32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J28" s="19">
         <f t="shared" si="2"/>
-        <v>47862.139999999992</v>
+        <v>0</v>
       </c>
       <c r="K28" s="19">
         <f t="shared" si="3"/>
@@ -4982,14 +5059,14 @@
       <c r="L28" s="88"/>
       <c r="M28" s="2">
         <f t="shared" si="4"/>
-        <v>499341.17449320736</v>
+        <v>442229.03449320735</v>
       </c>
       <c r="N28" s="5">
         <f t="shared" si="1"/>
-        <v>529301.64496279985</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+        <v>468762.77656279982</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -5004,21 +5081,22 @@
         <v>5.89</v>
       </c>
       <c r="F29" s="19">
-        <v>628440.74619410187</v>
-      </c>
-      <c r="G29" s="106">
-        <v>0</v>
+        <v>1129090.7461941019</v>
+      </c>
+      <c r="G29" s="160">
+        <f>1428000-G42-G43-G44</f>
+        <v>1154300</v>
       </c>
       <c r="H29" s="47">
         <f t="shared" si="0"/>
-        <v>628440.74619410187</v>
+        <v>-25209.25380589813</v>
       </c>
       <c r="I29" s="32">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J29" s="19">
         <f t="shared" si="2"/>
-        <v>47862.139999999992</v>
+        <v>0</v>
       </c>
       <c r="K29" s="19">
         <f t="shared" si="3"/>
@@ -5027,14 +5105,14 @@
       <c r="L29" s="88"/>
       <c r="M29" s="2">
         <f t="shared" si="4"/>
-        <v>1129090.7461941019</v>
+        <v>427578.60619410186</v>
       </c>
       <c r="N29" s="5">
         <f t="shared" si="1"/>
-        <v>1196836.1909657479</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>453233.32256574795</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="44" t="s">
         <v>69</v>
       </c>
@@ -5049,11 +5127,11 @@
         <v>0.54</v>
       </c>
       <c r="F30" s="19">
-        <v>45900</v>
-      </c>
-      <c r="G30" s="105">
+        <v>45900.000000000007</v>
+      </c>
+      <c r="G30" s="159">
         <f>F30</f>
-        <v>45900</v>
+        <v>45900.000000000007</v>
       </c>
       <c r="H30" s="46">
         <f t="shared" si="0"/>
@@ -5062,7 +5140,7 @@
       <c r="I30" s="32"/>
       <c r="J30" s="19">
         <f t="shared" si="2"/>
-        <v>4388.04</v>
+        <v>0</v>
       </c>
       <c r="K30" s="19">
         <f t="shared" si="3"/>
@@ -5071,14 +5149,14 @@
       <c r="L30" s="88"/>
       <c r="M30" s="2">
         <f t="shared" si="4"/>
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="N30" s="5">
         <f t="shared" si="1"/>
-        <v>48654.000000000007</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+        <v>44002.67760000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="44" t="s">
         <v>69</v>
       </c>
@@ -5095,7 +5173,7 @@
       <c r="F31" s="19">
         <v>46750</v>
       </c>
-      <c r="G31" s="105">
+      <c r="G31" s="159">
         <f>F31</f>
         <v>46750</v>
       </c>
@@ -5106,7 +5184,7 @@
       <c r="I31" s="32"/>
       <c r="J31" s="19">
         <f t="shared" si="2"/>
-        <v>4469.3</v>
+        <v>0</v>
       </c>
       <c r="K31" s="19">
         <f t="shared" si="3"/>
@@ -5115,14 +5193,14 @@
       <c r="L31" s="88"/>
       <c r="M31" s="2">
         <f t="shared" si="4"/>
-        <v>46750</v>
+        <v>42280.7</v>
       </c>
       <c r="N31" s="5">
         <f t="shared" si="1"/>
-        <v>49555</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+        <v>44817.541999999994</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="44" t="s">
         <v>69</v>
       </c>
@@ -5139,7 +5217,7 @@
       <c r="F32" s="19">
         <v>38250</v>
       </c>
-      <c r="G32" s="105">
+      <c r="G32" s="159">
         <f>F32</f>
         <v>38250</v>
       </c>
@@ -5150,7 +5228,7 @@
       <c r="I32" s="32"/>
       <c r="J32" s="19">
         <f t="shared" si="2"/>
-        <v>3656.7000000000003</v>
+        <v>0</v>
       </c>
       <c r="K32" s="19">
         <f t="shared" si="3"/>
@@ -5159,14 +5237,14 @@
       <c r="L32" s="68"/>
       <c r="M32" s="2">
         <f t="shared" si="4"/>
-        <v>38250</v>
+        <v>34593.300000000003</v>
       </c>
       <c r="N32" s="5">
         <f t="shared" si="1"/>
-        <v>40545</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+        <v>36668.898000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="44" t="s">
         <v>69</v>
       </c>
@@ -5183,7 +5261,7 @@
       <c r="F33" s="19">
         <v>51850</v>
       </c>
-      <c r="G33" s="105">
+      <c r="G33" s="159">
         <f t="shared" ref="G33" si="5">F33</f>
         <v>51850</v>
       </c>
@@ -5194,7 +5272,7 @@
       <c r="I33" s="32"/>
       <c r="J33" s="19">
         <f t="shared" si="2"/>
-        <v>4956.8599999999997</v>
+        <v>0</v>
       </c>
       <c r="K33" s="19">
         <f t="shared" si="3"/>
@@ -5203,14 +5281,14 @@
       <c r="L33" s="68"/>
       <c r="M33" s="2">
         <f t="shared" si="4"/>
-        <v>51850</v>
+        <v>46893.14</v>
       </c>
       <c r="N33" s="5">
         <f t="shared" si="1"/>
-        <v>54961</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+        <v>49706.7284</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="44" t="s">
         <v>69</v>
       </c>
@@ -5225,11 +5303,11 @@
         <v>0.54</v>
       </c>
       <c r="F34" s="19">
-        <v>45900</v>
-      </c>
-      <c r="G34" s="105">
+        <v>45900.000000000007</v>
+      </c>
+      <c r="G34" s="159">
         <f>F34</f>
-        <v>45900</v>
+        <v>45900.000000000007</v>
       </c>
       <c r="H34" s="46">
         <f t="shared" si="0"/>
@@ -5238,7 +5316,7 @@
       <c r="I34" s="32"/>
       <c r="J34" s="19">
         <f t="shared" si="2"/>
-        <v>4388.04</v>
+        <v>0</v>
       </c>
       <c r="K34" s="19">
         <f t="shared" si="3"/>
@@ -5247,14 +5325,14 @@
       <c r="L34" s="68"/>
       <c r="M34" s="2">
         <f t="shared" si="4"/>
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="N34" s="5">
         <f t="shared" si="1"/>
-        <v>48654.000000000007</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+        <v>44002.67760000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="44" t="s">
         <v>69</v>
       </c>
@@ -5271,18 +5349,15 @@
       <c r="F35" s="2">
         <v>42500</v>
       </c>
-      <c r="G35" s="106">
-        <f>F35</f>
-        <v>42500</v>
-      </c>
+      <c r="G35" s="105"/>
       <c r="H35" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42500</v>
       </c>
       <c r="I35" s="32"/>
       <c r="J35" s="19">
         <f t="shared" si="2"/>
-        <v>4063</v>
+        <v>0</v>
       </c>
       <c r="K35" s="19">
         <f t="shared" si="3"/>
@@ -5291,14 +5366,14 @@
       <c r="L35" s="68"/>
       <c r="M35" s="2">
         <f t="shared" si="4"/>
-        <v>42500</v>
+        <v>80937</v>
       </c>
       <c r="N35" s="5">
         <f t="shared" si="1"/>
-        <v>45050</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>85793.22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="44" t="s">
         <v>69</v>
       </c>
@@ -5315,7 +5390,7 @@
       <c r="F36" s="19">
         <v>42500</v>
       </c>
-      <c r="G36" s="105">
+      <c r="G36" s="159">
         <f>F36</f>
         <v>42500</v>
       </c>
@@ -5326,7 +5401,7 @@
       <c r="I36" s="32"/>
       <c r="J36" s="19">
         <f t="shared" si="2"/>
-        <v>4063</v>
+        <v>0</v>
       </c>
       <c r="K36" s="19">
         <f t="shared" si="3"/>
@@ -5335,14 +5410,14 @@
       <c r="L36" s="68"/>
       <c r="M36" s="2">
         <f t="shared" si="4"/>
-        <v>42500</v>
+        <v>38437</v>
       </c>
       <c r="N36" s="5">
         <f t="shared" si="1"/>
-        <v>45050</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>40743.22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="44" t="s">
         <v>69</v>
       </c>
@@ -5359,7 +5434,7 @@
       <c r="F37" s="19">
         <v>41650</v>
       </c>
-      <c r="G37" s="105">
+      <c r="G37" s="159">
         <f t="shared" ref="G37:G41" si="6">F37</f>
         <v>41650</v>
       </c>
@@ -5370,7 +5445,7 @@
       <c r="I37" s="32"/>
       <c r="J37" s="19">
         <f t="shared" si="2"/>
-        <v>3981.74</v>
+        <v>0</v>
       </c>
       <c r="K37" s="19">
         <f t="shared" si="3"/>
@@ -5379,14 +5454,14 @@
       <c r="L37" s="68"/>
       <c r="M37" s="2">
         <f t="shared" si="4"/>
-        <v>41650</v>
+        <v>37668.26</v>
       </c>
       <c r="N37" s="5">
         <f t="shared" si="1"/>
-        <v>44149</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+        <v>39928.355600000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="44" t="s">
         <v>69</v>
       </c>
@@ -5403,7 +5478,7 @@
       <c r="F38" s="19">
         <v>41650</v>
       </c>
-      <c r="G38" s="105">
+      <c r="G38" s="159">
         <f t="shared" si="6"/>
         <v>41650</v>
       </c>
@@ -5414,7 +5489,7 @@
       <c r="I38" s="32"/>
       <c r="J38" s="19">
         <f t="shared" si="2"/>
-        <v>3981.74</v>
+        <v>0</v>
       </c>
       <c r="K38" s="19">
         <f t="shared" si="3"/>
@@ -5423,14 +5498,14 @@
       <c r="L38" s="68"/>
       <c r="M38" s="2">
         <f t="shared" si="4"/>
-        <v>41650</v>
+        <v>37668.26</v>
       </c>
       <c r="N38" s="5">
         <f t="shared" si="1"/>
-        <v>44149</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+        <v>39928.355600000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="44" t="s">
         <v>69</v>
       </c>
@@ -5447,7 +5522,7 @@
       <c r="F39" s="19">
         <v>50150</v>
       </c>
-      <c r="G39" s="105">
+      <c r="G39" s="159">
         <f t="shared" si="6"/>
         <v>50150</v>
       </c>
@@ -5458,7 +5533,7 @@
       <c r="I39" s="32"/>
       <c r="J39" s="19">
         <f t="shared" si="2"/>
-        <v>4794.34</v>
+        <v>0</v>
       </c>
       <c r="K39" s="19">
         <f t="shared" si="3"/>
@@ -5467,14 +5542,14 @@
       <c r="L39" s="68"/>
       <c r="M39" s="2">
         <f t="shared" si="4"/>
-        <v>50150</v>
+        <v>45355.66</v>
       </c>
       <c r="N39" s="5">
         <f t="shared" si="1"/>
-        <v>53159</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+        <v>48076.999600000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="44" t="s">
         <v>69</v>
       </c>
@@ -5491,7 +5566,7 @@
       <c r="F40" s="19">
         <v>48450</v>
       </c>
-      <c r="G40" s="105">
+      <c r="G40" s="159">
         <f t="shared" si="6"/>
         <v>48450</v>
       </c>
@@ -5502,7 +5577,7 @@
       <c r="I40" s="32"/>
       <c r="J40" s="19">
         <f t="shared" si="2"/>
-        <v>4631.82</v>
+        <v>0</v>
       </c>
       <c r="K40" s="19">
         <f t="shared" si="3"/>
@@ -5511,14 +5586,14 @@
       <c r="L40" s="68"/>
       <c r="M40" s="2">
         <f t="shared" si="4"/>
-        <v>48450</v>
+        <v>43818.18</v>
       </c>
       <c r="N40" s="5">
         <f t="shared" si="1"/>
-        <v>51357</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+        <v>46447.270799999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="44" t="s">
         <v>69</v>
       </c>
@@ -5533,11 +5608,11 @@
         <v>0.54</v>
       </c>
       <c r="F41" s="19">
-        <v>45900</v>
-      </c>
-      <c r="G41" s="105">
+        <v>45900.000000000007</v>
+      </c>
+      <c r="G41" s="159">
         <f t="shared" si="6"/>
-        <v>45900</v>
+        <v>45900.000000000007</v>
       </c>
       <c r="H41" s="46">
         <f t="shared" si="0"/>
@@ -5546,7 +5621,7 @@
       <c r="I41" s="32"/>
       <c r="J41" s="19">
         <f t="shared" si="2"/>
-        <v>4388.04</v>
+        <v>0</v>
       </c>
       <c r="K41" s="19">
         <f t="shared" si="3"/>
@@ -5555,14 +5630,14 @@
       <c r="L41" s="68"/>
       <c r="M41" s="2">
         <f t="shared" si="4"/>
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="N41" s="5">
         <f t="shared" si="1"/>
-        <v>48654.000000000007</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+        <v>44002.67760000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="s">
         <v>69</v>
       </c>
@@ -5577,17 +5652,20 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="19">
-        <v>46750</v>
-      </c>
-      <c r="G42" s="105"/>
+        <v>93500</v>
+      </c>
+      <c r="G42" s="159">
+        <f>F42</f>
+        <v>93500</v>
+      </c>
       <c r="H42" s="46">
         <f t="shared" si="0"/>
-        <v>46750</v>
+        <v>0</v>
       </c>
       <c r="I42" s="32"/>
       <c r="J42" s="19">
         <f t="shared" si="2"/>
-        <v>4469.3</v>
+        <v>0</v>
       </c>
       <c r="K42" s="19">
         <f t="shared" si="3"/>
@@ -5596,14 +5674,14 @@
       <c r="L42" s="68"/>
       <c r="M42" s="2">
         <f t="shared" si="4"/>
-        <v>93500</v>
+        <v>42280.7</v>
       </c>
       <c r="N42" s="5">
         <f t="shared" si="1"/>
-        <v>99110</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+        <v>44817.541999999994</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>69</v>
       </c>
@@ -5618,17 +5696,20 @@
         <v>0.45</v>
       </c>
       <c r="F43" s="19">
-        <v>38250</v>
-      </c>
-      <c r="G43" s="105"/>
+        <v>76500</v>
+      </c>
+      <c r="G43" s="159">
+        <f>F43</f>
+        <v>76500</v>
+      </c>
       <c r="H43" s="46">
         <f t="shared" si="0"/>
-        <v>38250</v>
+        <v>0</v>
       </c>
       <c r="I43" s="32"/>
       <c r="J43" s="19">
         <f t="shared" si="2"/>
-        <v>3656.7000000000003</v>
+        <v>0</v>
       </c>
       <c r="K43" s="19">
         <f t="shared" si="3"/>
@@ -5637,18 +5718,18 @@
       <c r="L43" s="68"/>
       <c r="M43" s="2">
         <f t="shared" si="4"/>
-        <v>76500</v>
+        <v>34593.300000000003</v>
       </c>
       <c r="N43" s="5">
         <f t="shared" si="1"/>
-        <v>81090</v>
+        <v>36668.898000000001</v>
       </c>
       <c r="P43" s="34">
         <f>L1-K52</f>
-        <v>-1037439.8799579991</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>-412132.39995799866</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="44" t="s">
         <v>69</v>
       </c>
@@ -5663,17 +5744,20 @@
         <v>0.61</v>
       </c>
       <c r="F44" s="19">
-        <v>51850</v>
-      </c>
-      <c r="G44" s="105"/>
+        <v>103700</v>
+      </c>
+      <c r="G44" s="159">
+        <f>F44</f>
+        <v>103700</v>
+      </c>
       <c r="H44" s="46">
         <f t="shared" si="0"/>
-        <v>51850</v>
+        <v>0</v>
       </c>
       <c r="I44" s="32"/>
       <c r="J44" s="19">
         <f t="shared" si="2"/>
-        <v>4956.8599999999997</v>
+        <v>0</v>
       </c>
       <c r="K44" s="19">
         <f t="shared" si="3"/>
@@ -5682,14 +5766,14 @@
       <c r="L44" s="68"/>
       <c r="M44" s="2">
         <f t="shared" si="4"/>
-        <v>103700</v>
+        <v>46893.14</v>
       </c>
       <c r="N44" s="5">
         <f t="shared" si="1"/>
-        <v>109922</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+        <v>49706.7284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="44" t="s">
         <v>69</v>
       </c>
@@ -5704,11 +5788,11 @@
         <v>0.54</v>
       </c>
       <c r="F45" s="19">
-        <v>45900</v>
-      </c>
-      <c r="G45" s="105">
+        <v>45900.000000000007</v>
+      </c>
+      <c r="G45" s="159">
         <f t="shared" ref="G45" si="7">F45</f>
-        <v>45900</v>
+        <v>45900.000000000007</v>
       </c>
       <c r="H45" s="46">
         <f t="shared" si="0"/>
@@ -5717,7 +5801,7 @@
       <c r="I45" s="32"/>
       <c r="J45" s="19">
         <f t="shared" si="2"/>
-        <v>4388.04</v>
+        <v>0</v>
       </c>
       <c r="K45" s="19">
         <f t="shared" si="3"/>
@@ -5726,14 +5810,14 @@
       <c r="L45" s="68"/>
       <c r="M45" s="2">
         <f t="shared" si="4"/>
-        <v>45900.000000000007</v>
+        <v>41511.960000000006</v>
       </c>
       <c r="N45" s="5">
         <f t="shared" si="1"/>
-        <v>48654.000000000007</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+        <v>44002.67760000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="44" t="s">
         <v>69</v>
       </c>
@@ -5750,7 +5834,7 @@
       <c r="F46" s="19">
         <v>42500</v>
       </c>
-      <c r="G46" s="105">
+      <c r="G46" s="159">
         <f t="shared" ref="G46:G51" si="8">F46</f>
         <v>42500</v>
       </c>
@@ -5761,7 +5845,7 @@
       <c r="I46" s="32"/>
       <c r="J46" s="19">
         <f t="shared" si="2"/>
-        <v>4063</v>
+        <v>0</v>
       </c>
       <c r="K46" s="19">
         <f t="shared" si="3"/>
@@ -5770,17 +5854,17 @@
       <c r="L46" s="68"/>
       <c r="M46" s="2">
         <f t="shared" si="4"/>
-        <v>42500</v>
+        <v>38437</v>
       </c>
       <c r="N46" s="5">
         <f t="shared" si="1"/>
-        <v>45050</v>
+        <v>40743.22</v>
       </c>
       <c r="Q46" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="44" t="s">
         <v>69</v>
       </c>
@@ -5795,11 +5879,11 @@
         <v>0.5</v>
       </c>
       <c r="F47" s="19">
-        <v>42500</v>
-      </c>
-      <c r="G47" s="105">
+        <v>45050</v>
+      </c>
+      <c r="G47" s="159">
         <f t="shared" si="8"/>
-        <v>42500</v>
+        <v>45050</v>
       </c>
       <c r="H47" s="46">
         <f t="shared" si="0"/>
@@ -5808,7 +5892,7 @@
       <c r="I47" s="32"/>
       <c r="J47" s="19">
         <f t="shared" si="2"/>
-        <v>4063</v>
+        <v>0</v>
       </c>
       <c r="K47" s="19">
         <f t="shared" si="3"/>
@@ -5817,19 +5901,19 @@
       <c r="L47" s="68"/>
       <c r="M47" s="2">
         <f t="shared" si="4"/>
-        <v>42500</v>
+        <v>38437</v>
       </c>
       <c r="N47" s="5">
         <f t="shared" si="1"/>
-        <v>45050</v>
+        <v>40743.22</v>
       </c>
       <c r="O47" s="53"/>
       <c r="Q47" s="50">
         <f>M3-J52</f>
-        <v>65739.340000000084</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="44" t="s">
         <v>69</v>
       </c>
@@ -5844,11 +5928,11 @@
         <v>0.49</v>
       </c>
       <c r="F48" s="19">
-        <v>41650</v>
-      </c>
-      <c r="G48" s="105">
+        <v>44149</v>
+      </c>
+      <c r="G48" s="159">
         <f t="shared" si="8"/>
-        <v>41650</v>
+        <v>44149</v>
       </c>
       <c r="H48" s="46">
         <f t="shared" si="0"/>
@@ -5857,7 +5941,7 @@
       <c r="I48" s="32"/>
       <c r="J48" s="19">
         <f t="shared" si="2"/>
-        <v>3981.74</v>
+        <v>0</v>
       </c>
       <c r="K48" s="19">
         <f t="shared" si="3"/>
@@ -5866,14 +5950,14 @@
       <c r="L48" s="68"/>
       <c r="M48" s="2">
         <f t="shared" si="4"/>
-        <v>41650</v>
+        <v>37668.26</v>
       </c>
       <c r="N48" s="5">
         <f t="shared" si="1"/>
-        <v>44149</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+        <v>39928.355600000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="44" t="s">
         <v>69</v>
       </c>
@@ -5891,7 +5975,7 @@
       <c r="F49" s="19">
         <v>41650</v>
       </c>
-      <c r="G49" s="105">
+      <c r="G49" s="159">
         <f t="shared" si="8"/>
         <v>41650</v>
       </c>
@@ -5902,7 +5986,7 @@
       <c r="I49" s="32"/>
       <c r="J49" s="19">
         <f t="shared" si="2"/>
-        <v>3981.74</v>
+        <v>0</v>
       </c>
       <c r="K49" s="19">
         <f t="shared" si="3"/>
@@ -5911,14 +5995,14 @@
       <c r="L49" s="68"/>
       <c r="M49" s="2">
         <f t="shared" si="4"/>
-        <v>41650</v>
+        <v>37668.26</v>
       </c>
       <c r="N49" s="5">
         <f t="shared" si="1"/>
-        <v>44149</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+        <v>39928.355600000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="44" t="s">
         <v>69</v>
       </c>
@@ -5935,7 +6019,7 @@
       <c r="F50" s="19">
         <v>50150</v>
       </c>
-      <c r="G50" s="106">
+      <c r="G50" s="160">
         <f t="shared" si="8"/>
         <v>50150</v>
       </c>
@@ -5946,7 +6030,7 @@
       <c r="I50" s="32"/>
       <c r="J50" s="19">
         <f t="shared" si="2"/>
-        <v>4794.34</v>
+        <v>0</v>
       </c>
       <c r="K50" s="19">
         <f t="shared" si="3"/>
@@ -5955,14 +6039,14 @@
       <c r="L50" s="68"/>
       <c r="M50" s="2">
         <f t="shared" si="4"/>
-        <v>50150</v>
+        <v>45355.66</v>
       </c>
       <c r="N50" s="5">
         <f t="shared" si="1"/>
-        <v>53159</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+        <v>48076.999600000003</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="44" t="s">
         <v>69</v>
       </c>
@@ -5979,7 +6063,7 @@
       <c r="F51" s="19">
         <v>48450</v>
       </c>
-      <c r="G51" s="105">
+      <c r="G51" s="159">
         <f t="shared" si="8"/>
         <v>48450</v>
       </c>
@@ -5990,7 +6074,7 @@
       <c r="I51" s="32"/>
       <c r="J51" s="19">
         <f t="shared" si="2"/>
-        <v>4631.82</v>
+        <v>0</v>
       </c>
       <c r="K51" s="19">
         <f t="shared" si="3"/>
@@ -5999,14 +6083,14 @@
       <c r="L51" s="68"/>
       <c r="M51" s="2">
         <f t="shared" si="4"/>
-        <v>48450</v>
+        <v>43818.18</v>
       </c>
       <c r="N51" s="5">
         <f t="shared" si="1"/>
-        <v>51357</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>46447.270799999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="20"/>
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
@@ -6017,17 +6101,17 @@
       </c>
       <c r="F52" s="85">
         <f>SUM(F7:F51)</f>
-        <v>7157130.5960010365</v>
+        <v>6554076.3145067021</v>
       </c>
       <c r="G52" s="85">
         <f>SUM(G7:G51)</f>
-        <v>8886432.0578930005</v>
+        <v>7986260.3999579996</v>
       </c>
       <c r="H52" s="20"/>
       <c r="I52" s="20"/>
       <c r="J52" s="45">
         <f>SUM(J8:J51)</f>
-        <v>746860.65999999992</v>
+        <v>0</v>
       </c>
       <c r="K52" s="21">
         <f>SUM(K7:K51)</f>
@@ -6035,53 +6119,53 @@
       </c>
       <c r="L52" s="87">
         <f>SUM(L7:L51)</f>
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="M52" s="22">
         <f>SUM(M7:M51)</f>
-        <v>6499211.0980660357</v>
+        <v>5943728.4745067004</v>
       </c>
       <c r="N52" s="21">
         <f>SUM(N7:N51)</f>
-        <v>6889163.7639499977</v>
+        <v>6300352.1829771074</v>
       </c>
       <c r="P52" s="50"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="53">
         <f>K52-L1</f>
-        <v>1037439.8799579991</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="185"/>
-      <c r="D54" s="185"/>
-      <c r="E54" s="185"/>
-      <c r="F54" s="185"/>
-      <c r="G54" s="185"/>
-      <c r="H54" s="185"/>
-      <c r="I54" s="185"/>
-      <c r="J54" s="185"/>
-      <c r="K54" s="185"/>
-      <c r="L54" s="185"/>
-      <c r="M54" s="185"/>
-      <c r="N54" s="185"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="185"/>
-      <c r="D55" s="185"/>
-      <c r="E55" s="185"/>
-      <c r="F55" s="185"/>
-      <c r="G55" s="185"/>
-      <c r="H55" s="185"/>
-      <c r="I55" s="185"/>
-      <c r="J55" s="185"/>
-      <c r="K55" s="185"/>
-      <c r="L55" s="185"/>
-      <c r="M55" s="185"/>
-      <c r="N55" s="185"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+        <v>412132.39995799866</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="215"/>
+      <c r="D54" s="215"/>
+      <c r="E54" s="215"/>
+      <c r="F54" s="215"/>
+      <c r="G54" s="215"/>
+      <c r="H54" s="215"/>
+      <c r="I54" s="215"/>
+      <c r="J54" s="215"/>
+      <c r="K54" s="215"/>
+      <c r="L54" s="215"/>
+      <c r="M54" s="215"/>
+      <c r="N54" s="215"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="215"/>
+      <c r="D55" s="215"/>
+      <c r="E55" s="215"/>
+      <c r="F55" s="215"/>
+      <c r="G55" s="215"/>
+      <c r="H55" s="215"/>
+      <c r="I55" s="215"/>
+      <c r="J55" s="215"/>
+      <c r="K55" s="215"/>
+      <c r="L55" s="215"/>
+      <c r="M55" s="215"/>
+      <c r="N55" s="215"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="70"/>
       <c r="D56" s="70"/>
       <c r="E56" s="70"/>
@@ -6095,112 +6179,108 @@
       <c r="M56" s="70"/>
       <c r="N56" s="70"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="185" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C57" s="215" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="185"/>
-      <c r="E57" s="185"/>
-      <c r="F57" s="185"/>
-      <c r="G57" s="185"/>
-      <c r="H57" s="185"/>
-      <c r="I57" s="185"/>
-      <c r="J57" s="185"/>
-      <c r="K57" s="185"/>
-      <c r="L57" s="185"/>
-      <c r="M57" s="185"/>
-      <c r="N57" s="185"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="185"/>
-      <c r="D58" s="185"/>
-      <c r="E58" s="185"/>
-      <c r="F58" s="185"/>
-      <c r="G58" s="185"/>
-      <c r="H58" s="185"/>
-      <c r="I58" s="185"/>
-      <c r="J58" s="185"/>
-      <c r="K58" s="185"/>
-      <c r="L58" s="185"/>
-      <c r="M58" s="185"/>
-      <c r="N58" s="185"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="185"/>
-      <c r="D59" s="185"/>
-      <c r="E59" s="185"/>
-      <c r="F59" s="185"/>
-      <c r="G59" s="185"/>
-      <c r="H59" s="185"/>
-      <c r="I59" s="185"/>
-      <c r="J59" s="185"/>
-      <c r="K59" s="185"/>
-      <c r="L59" s="185"/>
-      <c r="M59" s="185"/>
-      <c r="N59" s="185"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="185"/>
-      <c r="D60" s="185"/>
-      <c r="E60" s="185"/>
-      <c r="F60" s="185"/>
-      <c r="G60" s="185"/>
-      <c r="H60" s="185"/>
-      <c r="I60" s="185"/>
-      <c r="J60" s="185"/>
-      <c r="K60" s="185"/>
-      <c r="L60" s="185"/>
-      <c r="M60" s="185"/>
-      <c r="N60" s="185"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="185"/>
-      <c r="D61" s="185"/>
-      <c r="E61" s="185"/>
-      <c r="F61" s="185"/>
-      <c r="G61" s="185"/>
-      <c r="H61" s="185"/>
-      <c r="I61" s="185"/>
-      <c r="J61" s="185"/>
-      <c r="K61" s="185"/>
-      <c r="L61" s="185"/>
-      <c r="M61" s="185"/>
-      <c r="N61" s="185"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="185"/>
-      <c r="D62" s="185"/>
-      <c r="E62" s="185"/>
-      <c r="F62" s="185"/>
-      <c r="G62" s="185"/>
-      <c r="H62" s="185"/>
-      <c r="I62" s="185"/>
-      <c r="J62" s="185"/>
-      <c r="K62" s="185"/>
-      <c r="L62" s="185"/>
-      <c r="M62" s="185"/>
-      <c r="N62" s="185"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="185"/>
-      <c r="D63" s="185"/>
-      <c r="E63" s="185"/>
-      <c r="F63" s="185"/>
-      <c r="G63" s="185"/>
-      <c r="H63" s="185"/>
-      <c r="I63" s="185"/>
-      <c r="J63" s="185"/>
-      <c r="K63" s="185"/>
-      <c r="L63" s="185"/>
-      <c r="M63" s="185"/>
-      <c r="N63" s="185"/>
+      <c r="D57" s="215"/>
+      <c r="E57" s="215"/>
+      <c r="F57" s="215"/>
+      <c r="G57" s="215"/>
+      <c r="H57" s="215"/>
+      <c r="I57" s="215"/>
+      <c r="J57" s="215"/>
+      <c r="K57" s="215"/>
+      <c r="L57" s="215"/>
+      <c r="M57" s="215"/>
+      <c r="N57" s="215"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C58" s="215"/>
+      <c r="D58" s="215"/>
+      <c r="E58" s="215"/>
+      <c r="F58" s="215"/>
+      <c r="G58" s="215"/>
+      <c r="H58" s="215"/>
+      <c r="I58" s="215"/>
+      <c r="J58" s="215"/>
+      <c r="K58" s="215"/>
+      <c r="L58" s="215"/>
+      <c r="M58" s="215"/>
+      <c r="N58" s="215"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C59" s="215"/>
+      <c r="D59" s="215"/>
+      <c r="E59" s="215"/>
+      <c r="F59" s="215"/>
+      <c r="G59" s="215"/>
+      <c r="H59" s="215"/>
+      <c r="I59" s="215"/>
+      <c r="J59" s="215"/>
+      <c r="K59" s="215"/>
+      <c r="L59" s="215"/>
+      <c r="M59" s="215"/>
+      <c r="N59" s="215"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C60" s="215"/>
+      <c r="D60" s="215"/>
+      <c r="E60" s="215"/>
+      <c r="F60" s="215"/>
+      <c r="G60" s="215"/>
+      <c r="H60" s="215"/>
+      <c r="I60" s="215"/>
+      <c r="J60" s="215"/>
+      <c r="K60" s="215"/>
+      <c r="L60" s="215"/>
+      <c r="M60" s="215"/>
+      <c r="N60" s="215"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C61" s="215"/>
+      <c r="D61" s="215"/>
+      <c r="E61" s="215"/>
+      <c r="F61" s="215"/>
+      <c r="G61" s="215"/>
+      <c r="H61" s="215"/>
+      <c r="I61" s="215"/>
+      <c r="J61" s="215"/>
+      <c r="K61" s="215"/>
+      <c r="L61" s="215"/>
+      <c r="M61" s="215"/>
+      <c r="N61" s="215"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C62" s="215"/>
+      <c r="D62" s="215"/>
+      <c r="E62" s="215"/>
+      <c r="F62" s="215"/>
+      <c r="G62" s="215"/>
+      <c r="H62" s="215"/>
+      <c r="I62" s="215"/>
+      <c r="J62" s="215"/>
+      <c r="K62" s="215"/>
+      <c r="L62" s="215"/>
+      <c r="M62" s="215"/>
+      <c r="N62" s="215"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C63" s="215"/>
+      <c r="D63" s="215"/>
+      <c r="E63" s="215"/>
+      <c r="F63" s="215"/>
+      <c r="G63" s="215"/>
+      <c r="H63" s="215"/>
+      <c r="I63" s="215"/>
+      <c r="J63" s="215"/>
+      <c r="K63" s="215"/>
+      <c r="L63" s="215"/>
+      <c r="M63" s="215"/>
+      <c r="N63" s="215"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
@@ -6215,6 +6295,10 @@
     <mergeCell ref="A1:J4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6224,9 +6308,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2666E70F-CDC7-456F-AF96-2906778A9145}">
   <dimension ref="C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>119</v>
       </c>

--- a/2026/BELGRANO 1646/Mayo/Mayo-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Mayo/Mayo-BLG1646.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8CA3D4-8F47-49EB-99FE-41E95D18CCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB214C37-AABA-484F-BD6E-333F82687568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$125</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$124</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="147">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -498,9 +498,6 @@
   </si>
   <si>
     <t>SA Seguridad - Emergencia porton rejas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Servisur - cambio de luminarias </t>
   </si>
   <si>
     <t>-</t>
@@ -1088,7 +1085,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="210">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1264,9 +1261,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1285,23 +1279,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1391,6 +1376,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1403,12 +1397,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1460,10 +1448,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1863,7 +1847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N135"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -1882,13 +1866,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="90"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="155" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="162"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="156"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
@@ -1992,29 +1976,29 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="78"/>
-      <c r="B14" s="165" t="s">
+      <c r="B14" s="159" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="166"/>
-      <c r="D14" s="167"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="161"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="78"/>
-      <c r="B15" s="168"/>
-      <c r="C15" s="169"/>
-      <c r="D15" s="170"/>
+      <c r="B15" s="162"/>
+      <c r="C15" s="163"/>
+      <c r="D15" s="164"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="78"/>
-      <c r="B16" s="168"/>
-      <c r="C16" s="169"/>
-      <c r="D16" s="170"/>
+      <c r="B16" s="162"/>
+      <c r="C16" s="163"/>
+      <c r="D16" s="164"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="78"/>
-      <c r="B17" s="171"/>
-      <c r="C17" s="172"/>
-      <c r="D17" s="173"/>
+      <c r="B17" s="165"/>
+      <c r="C17" s="166"/>
+      <c r="D17" s="167"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="78"/>
@@ -2056,7 +2040,7 @@
         <v>123</v>
       </c>
       <c r="C22" s="79"/>
-      <c r="D22" s="151"/>
+      <c r="D22" s="150"/>
       <c r="E22" s="82"/>
       <c r="F22" s="82"/>
     </row>
@@ -2066,7 +2050,7 @@
       </c>
       <c r="B23" s="79"/>
       <c r="C23" s="79"/>
-      <c r="D23" s="157">
+      <c r="D23" s="102">
         <v>1575703.3</v>
       </c>
       <c r="E23" s="49">
@@ -2084,7 +2068,7 @@
       </c>
       <c r="B24" s="79"/>
       <c r="C24" s="79"/>
-      <c r="D24" s="157">
+      <c r="D24" s="102">
         <v>-342715.56</v>
       </c>
       <c r="E24" s="49">
@@ -2103,7 +2087,7 @@
       </c>
       <c r="B25" s="79"/>
       <c r="C25" s="79"/>
-      <c r="D25" s="157">
+      <c r="D25" s="102">
         <v>0.16</v>
       </c>
       <c r="E25" s="49">
@@ -2401,7 +2385,7 @@
       </c>
       <c r="B44" s="79"/>
       <c r="C44" s="101"/>
-      <c r="D44" s="155">
+      <c r="D44" s="37">
         <v>6642</v>
       </c>
       <c r="E44" s="49">
@@ -2422,7 +2406,7 @@
         <v>120</v>
       </c>
       <c r="C45" s="79"/>
-      <c r="D45" s="155">
+      <c r="D45" s="37">
         <f>75057.3+8339.7+151650.1</f>
         <v>235047.1</v>
       </c>
@@ -2444,7 +2428,7 @@
         <v>139</v>
       </c>
       <c r="C46" s="79"/>
-      <c r="D46" s="155">
+      <c r="D46" s="37">
         <v>739569.96</v>
       </c>
       <c r="E46" s="49">
@@ -2501,7 +2485,7 @@
       </c>
       <c r="B49" s="79"/>
       <c r="C49" s="79"/>
-      <c r="D49" s="155">
+      <c r="D49" s="37">
         <v>434000</v>
       </c>
       <c r="E49" s="60">
@@ -2529,7 +2513,7 @@
       </c>
       <c r="B50" s="79"/>
       <c r="C50" s="79"/>
-      <c r="D50" s="155">
+      <c r="D50" s="37">
         <v>380000</v>
       </c>
       <c r="E50" s="60">
@@ -2548,44 +2532,43 @@
       </c>
       <c r="B51" s="126"/>
       <c r="C51" s="79"/>
-      <c r="D51" s="155">
+      <c r="D51" s="37">
         <v>255779</v>
       </c>
       <c r="E51" s="60">
-        <f t="shared" ref="E51:E59" si="7">D51*91.91%</f>
+        <f t="shared" ref="E51:E58" si="7">D51*91.91%</f>
         <v>235086.47889999999</v>
       </c>
       <c r="F51" s="49">
-        <f t="shared" ref="F51:F59" si="8">D51*8.09%</f>
+        <f t="shared" ref="F51:F58" si="8">D51*8.09%</f>
         <v>20692.521099999998</v>
       </c>
       <c r="G51" s="34">
-        <f t="shared" ref="G51:G70" si="9">D51</f>
+        <f t="shared" ref="G51:G69" si="9">D51</f>
         <v>255779</v>
       </c>
       <c r="H51" s="67">
-        <f t="shared" ref="H51:H70" si="10">E51+F51</f>
+        <f t="shared" ref="H51:H69" si="10">E51+F51</f>
         <v>255779</v>
       </c>
       <c r="I51" s="76"/>
       <c r="J51" s="76"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="119" t="s">
+      <c r="A52" s="79" t="s">
         <v>134</v>
       </c>
       <c r="B52" s="79"/>
       <c r="C52" s="79"/>
-      <c r="D52" s="155">
+      <c r="D52" s="37">
         <v>59169</v>
       </c>
       <c r="E52" s="60">
-        <f t="shared" si="7"/>
-        <v>54382.227899999998</v>
+        <f>D52</f>
+        <v>59169</v>
       </c>
       <c r="F52" s="49">
-        <f t="shared" si="8"/>
-        <v>4786.7721000000001</v>
+        <v>0</v>
       </c>
       <c r="G52" s="34">
         <f t="shared" si="9"/>
@@ -2599,21 +2582,20 @@
       <c r="J52" s="76"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="119" t="s">
+      <c r="A53" s="79" t="s">
         <v>144</v>
       </c>
       <c r="B53" s="79"/>
       <c r="C53" s="79"/>
-      <c r="D53" s="155">
+      <c r="D53" s="37">
         <v>108900</v>
       </c>
       <c r="E53" s="60">
-        <f t="shared" si="7"/>
-        <v>100089.98999999999</v>
+        <f>D53</f>
+        <v>108900</v>
       </c>
       <c r="F53" s="49">
-        <f t="shared" si="8"/>
-        <v>8810.01</v>
+        <v>0</v>
       </c>
       <c r="G53" s="34"/>
       <c r="H53" s="67"/>
@@ -2626,7 +2608,7 @@
       </c>
       <c r="B54" s="79"/>
       <c r="C54" s="79"/>
-      <c r="D54" s="155">
+      <c r="D54" s="37">
         <v>205404</v>
       </c>
       <c r="E54" s="60">
@@ -2658,7 +2640,7 @@
       <c r="C55" s="79" t="s">
         <v>141</v>
       </c>
-      <c r="D55" s="155">
+      <c r="D55" s="37">
         <v>129315.21</v>
       </c>
       <c r="E55" s="60">
@@ -2678,11 +2660,11 @@
         <v>129315.21</v>
       </c>
       <c r="I55" s="76">
-        <f t="shared" ref="I55:I70" si="15">H55-D55</f>
+        <f t="shared" ref="I55:I69" si="15">H55-D55</f>
         <v>0</v>
       </c>
       <c r="J55" s="76">
-        <f t="shared" ref="J55:J70" si="16">G55-D55</f>
+        <f t="shared" ref="J55:J69" si="16">G55-D55</f>
         <v>0</v>
       </c>
     </row>
@@ -2694,7 +2676,7 @@
         <v>132</v>
       </c>
       <c r="C56" s="79"/>
-      <c r="D56" s="155">
+      <c r="D56" s="37">
         <v>353513.62</v>
       </c>
       <c r="E56" s="60">
@@ -2728,7 +2710,7 @@
       </c>
       <c r="B57" s="79"/>
       <c r="C57" s="79"/>
-      <c r="D57" s="155">
+      <c r="D57" s="37">
         <v>544500</v>
       </c>
       <c r="E57" s="60">
@@ -2756,7 +2738,7 @@
       </c>
       <c r="B58" s="101"/>
       <c r="C58" s="101"/>
-      <c r="D58" s="155">
+      <c r="D58" s="37">
         <v>37141.58</v>
       </c>
       <c r="E58" s="60">
@@ -2785,21 +2767,20 @@
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="120" t="s">
-        <v>147</v>
-      </c>
-      <c r="B59" s="141"/>
-      <c r="C59" s="216"/>
-      <c r="D59" s="155">
+      <c r="A59" s="101" t="s">
+        <v>146</v>
+      </c>
+      <c r="B59" s="140"/>
+      <c r="C59" s="152"/>
+      <c r="D59" s="37">
         <v>150000</v>
       </c>
       <c r="E59" s="60">
-        <f t="shared" si="7"/>
-        <v>137865</v>
+        <f>D59</f>
+        <v>150000</v>
       </c>
       <c r="F59" s="49">
-        <f t="shared" si="8"/>
-        <v>12135</v>
+        <v>0</v>
       </c>
       <c r="G59" s="34">
         <f t="shared" si="9"/>
@@ -2816,9 +2797,9 @@
       <c r="A60" s="127" t="s">
         <v>125</v>
       </c>
-      <c r="B60" s="142"/>
-      <c r="C60" s="143"/>
-      <c r="D60" s="155">
+      <c r="B60" s="141"/>
+      <c r="C60" s="142"/>
+      <c r="D60" s="37">
         <v>62000</v>
       </c>
       <c r="E60" s="60">
@@ -2838,12 +2819,12 @@
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="156" t="s">
+      <c r="A61" s="151" t="s">
         <v>140</v>
       </c>
-      <c r="B61" s="142"/>
-      <c r="C61" s="143"/>
-      <c r="D61" s="155">
+      <c r="B61" s="141"/>
+      <c r="C61" s="142"/>
+      <c r="D61" s="37">
         <v>90000</v>
       </c>
       <c r="E61" s="60">
@@ -2860,26 +2841,29 @@
       <c r="J61" s="76"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="139" t="s">
+      <c r="A62" s="153" t="s">
         <v>133</v>
       </c>
       <c r="B62" s="128"/>
       <c r="C62" s="129"/>
-      <c r="D62" s="155">
+      <c r="D62" s="37">
         <v>55000</v>
       </c>
       <c r="E62" s="60">
-        <f t="shared" ref="E62:E67" si="18">D62</f>
-        <v>55000</v>
-      </c>
-      <c r="F62" s="49"/>
+        <f t="shared" ref="E62" si="18">D62*91.91%</f>
+        <v>50550.499999999993</v>
+      </c>
+      <c r="F62" s="49">
+        <f t="shared" ref="F62" si="19">D62*8.09%</f>
+        <v>4449.5</v>
+      </c>
       <c r="G62" s="34">
         <f t="shared" si="9"/>
         <v>55000</v>
       </c>
       <c r="H62" s="67">
         <f t="shared" si="10"/>
-        <v>55000</v>
+        <v>54999.999999999993</v>
       </c>
       <c r="I62" s="76">
         <f t="shared" si="15"/>
@@ -2891,16 +2875,16 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="188" t="s">
+      <c r="A63" s="182" t="s">
         <v>129</v>
       </c>
-      <c r="B63" s="189"/>
-      <c r="C63" s="190"/>
-      <c r="D63" s="155">
+      <c r="B63" s="183"/>
+      <c r="C63" s="184"/>
+      <c r="D63" s="37">
         <v>420000</v>
       </c>
       <c r="E63" s="60">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="E63:E66" si="20">D63</f>
         <v>420000</v>
       </c>
       <c r="F63" s="49"/>
@@ -2919,16 +2903,16 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="191" t="s">
+      <c r="A64" s="185" t="s">
         <v>130</v>
       </c>
-      <c r="B64" s="186"/>
-      <c r="C64" s="187"/>
-      <c r="D64" s="155">
+      <c r="B64" s="180"/>
+      <c r="C64" s="181"/>
+      <c r="D64" s="37">
         <v>90000</v>
       </c>
       <c r="E64" s="60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>90000</v>
       </c>
       <c r="F64" s="49"/>
@@ -2946,23 +2930,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="154" t="s">
-        <v>145</v>
-      </c>
-      <c r="B65" s="152"/>
-      <c r="C65" s="153"/>
-      <c r="D65" s="155">
-        <v>120000</v>
+    <row r="65" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="185" t="s">
+        <v>137</v>
+      </c>
+      <c r="B65" s="180"/>
+      <c r="C65" s="181"/>
+      <c r="D65" s="37">
+        <v>70000</v>
       </c>
       <c r="E65" s="60">
-        <f t="shared" si="18"/>
-        <v>120000</v>
+        <f t="shared" si="20"/>
+        <v>70000</v>
       </c>
       <c r="F65" s="49"/>
       <c r="G65" s="34">
         <f t="shared" si="9"/>
-        <v>120000</v>
+        <v>70000</v>
       </c>
       <c r="H65" s="67"/>
       <c r="I65" s="76"/>
@@ -2971,79 +2955,87 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="191" t="s">
-        <v>137</v>
-      </c>
-      <c r="B66" s="186"/>
-      <c r="C66" s="187"/>
-      <c r="D66" s="155">
-        <v>70000</v>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="182" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" s="183"/>
+      <c r="C66" s="184"/>
+      <c r="D66" s="37">
+        <v>33000</v>
       </c>
       <c r="E66" s="60">
-        <f t="shared" si="18"/>
-        <v>70000</v>
-      </c>
-      <c r="F66" s="49"/>
+        <f t="shared" si="20"/>
+        <v>33000</v>
+      </c>
+      <c r="F66" s="49">
+        <v>0</v>
+      </c>
       <c r="G66" s="34">
+        <f t="shared" ref="G66" si="21">D66</f>
+        <v>33000</v>
+      </c>
+      <c r="H66" s="67">
+        <f t="shared" ref="H66" si="22">E66+F66</f>
+        <v>33000</v>
+      </c>
+      <c r="I66" s="76"/>
+      <c r="J66" s="76"/>
+    </row>
+    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="182" t="s">
+        <v>138</v>
+      </c>
+      <c r="B67" s="183"/>
+      <c r="C67" s="184"/>
+      <c r="D67" s="37">
+        <v>25200</v>
+      </c>
+      <c r="E67" s="60">
+        <f t="shared" ref="E67:E69" si="23">D67</f>
+        <v>25200</v>
+      </c>
+      <c r="F67" s="49"/>
+      <c r="G67" s="34">
         <f t="shared" si="9"/>
-        <v>70000</v>
-      </c>
-      <c r="H66" s="67"/>
-      <c r="I66" s="76"/>
-      <c r="J66" s="76">
+        <v>25200</v>
+      </c>
+      <c r="H67" s="67">
+        <f t="shared" si="10"/>
+        <v>25200</v>
+      </c>
+      <c r="I67" s="76">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="76">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="188" t="s">
-        <v>131</v>
-      </c>
-      <c r="B67" s="189"/>
-      <c r="C67" s="190"/>
-      <c r="D67" s="155">
-        <v>33000</v>
-      </c>
-      <c r="E67" s="60">
-        <f t="shared" si="18"/>
-        <v>33000</v>
-      </c>
-      <c r="F67" s="49">
-        <v>0</v>
-      </c>
-      <c r="G67" s="34">
-        <f t="shared" ref="G67" si="19">D67</f>
-        <v>33000</v>
-      </c>
-      <c r="H67" s="67">
-        <f t="shared" ref="H67" si="20">E67+F67</f>
-        <v>33000</v>
-      </c>
-      <c r="I67" s="76"/>
-      <c r="J67" s="76"/>
-    </row>
     <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="188" t="s">
-        <v>138</v>
-      </c>
-      <c r="B68" s="189"/>
-      <c r="C68" s="190"/>
-      <c r="D68" s="155">
-        <v>25200</v>
+      <c r="A68" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68" s="124" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" s="139"/>
+      <c r="D68" s="37">
+        <v>103395</v>
       </c>
       <c r="E68" s="60">
-        <f t="shared" ref="E68:E70" si="21">D68</f>
-        <v>25200</v>
+        <f t="shared" si="23"/>
+        <v>103395</v>
       </c>
       <c r="F68" s="49"/>
       <c r="G68" s="34">
         <f t="shared" si="9"/>
-        <v>25200</v>
+        <v>103395</v>
       </c>
       <c r="H68" s="67">
         <f t="shared" si="10"/>
-        <v>25200</v>
+        <v>103395</v>
       </c>
       <c r="I68" s="76">
         <f t="shared" si="15"/>
@@ -3054,29 +3046,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="B69" s="124" t="s">
-        <v>126</v>
-      </c>
-      <c r="C69" s="140"/>
-      <c r="D69" s="155">
-        <v>103395</v>
-      </c>
+    <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="179"/>
+      <c r="B69" s="180"/>
+      <c r="C69" s="181"/>
+      <c r="D69" s="37"/>
       <c r="E69" s="60">
-        <f t="shared" si="21"/>
-        <v>103395</v>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="F69" s="49"/>
       <c r="G69" s="34">
         <f t="shared" si="9"/>
-        <v>103395</v>
+        <v>0</v>
       </c>
       <c r="H69" s="67">
         <f t="shared" si="10"/>
-        <v>103395</v>
+        <v>0</v>
       </c>
       <c r="I69" s="76">
         <f t="shared" si="15"/>
@@ -3087,70 +3073,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="185"/>
-      <c r="B70" s="186"/>
-      <c r="C70" s="187"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="60">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="F70" s="49"/>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="118" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" s="122"/>
+      <c r="C70" s="122"/>
+      <c r="D70" s="33">
+        <f>SUM(D49:D69)</f>
+        <v>3606317.41</v>
+      </c>
+      <c r="E70" s="33">
+        <f>SUM(E49:E69)</f>
+        <v>3478442.5491309999</v>
+      </c>
+      <c r="F70" s="33">
+        <f>SUM(F49:F69)</f>
+        <v>127874.86086900001</v>
+      </c>
       <c r="G70" s="34">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H70" s="67">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>E70+F70</f>
+        <v>3606317.41</v>
+      </c>
+      <c r="H70" s="61" t="str">
+        <f>IF(D70=G70, "", "Error")</f>
+        <v/>
       </c>
       <c r="I70" s="76">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J70" s="76">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="118" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="122"/>
-      <c r="C71" s="122"/>
-      <c r="D71" s="33">
-        <f>SUM(D49:D70)</f>
-        <v>3726317.41</v>
-      </c>
-      <c r="E71" s="33">
-        <f>SUM(E49:E70)</f>
-        <v>3577160.2670309995</v>
-      </c>
-      <c r="F71" s="33">
-        <f>SUM(F49:F70)</f>
-        <v>149157.14296900001</v>
-      </c>
-      <c r="G71" s="34">
-        <f>E71+F71</f>
-        <v>3726317.4099999997</v>
-      </c>
-      <c r="H71" s="61" t="str">
-        <f>IF(D71=G71, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I71" s="76">
-        <f>D71-G71</f>
-        <v>0</v>
-      </c>
+        <f>D70-G70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="79"/>
+      <c r="B71" s="79"/>
+      <c r="C71" s="79"/>
+      <c r="D71" s="104"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="3"/>
+      <c r="H71" s="61"/>
     </row>
     <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="79"/>
       <c r="B72" s="79"/>
       <c r="C72" s="79"/>
       <c r="D72" s="104"/>
-      <c r="E72" s="39"/>
+      <c r="E72" s="38"/>
       <c r="F72" s="3"/>
       <c r="H72" s="61"/>
     </row>
@@ -3163,113 +3131,115 @@
       <c r="F73" s="3"/>
       <c r="H73" s="61"/>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="79"/>
-      <c r="B74" s="79"/>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="120" t="s">
+        <v>143</v>
+      </c>
+      <c r="B74" s="101"/>
       <c r="C74" s="79"/>
-      <c r="D74" s="104"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="3"/>
+      <c r="D74" s="37">
+        <v>252200</v>
+      </c>
+      <c r="E74" s="60">
+        <f>D74*91.91%</f>
+        <v>231797.02</v>
+      </c>
+      <c r="F74" s="49">
+        <f>D74*8.09%</f>
+        <v>20402.98</v>
+      </c>
+      <c r="G74" s="66"/>
       <c r="H74" s="61"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="120" t="s">
         <v>143</v>
       </c>
-      <c r="B75" s="101"/>
-      <c r="C75" s="79"/>
-      <c r="D75" s="155">
-        <v>252200</v>
+      <c r="B75" s="140"/>
+      <c r="C75" s="125"/>
+      <c r="D75" s="37">
+        <v>155650</v>
       </c>
       <c r="E75" s="60">
         <f>D75*91.91%</f>
-        <v>231797.02</v>
+        <v>143057.91499999998</v>
       </c>
       <c r="F75" s="49">
         <f>D75*8.09%</f>
-        <v>20402.98</v>
+        <v>12592.084999999999</v>
       </c>
       <c r="G75" s="66"/>
       <c r="H75" s="61"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="120" t="s">
-        <v>143</v>
-      </c>
-      <c r="B76" s="141"/>
+      <c r="A76" s="101" t="s">
+        <v>142</v>
+      </c>
+      <c r="B76" s="140"/>
       <c r="C76" s="125"/>
-      <c r="D76" s="155">
-        <v>155650</v>
+      <c r="D76" s="37">
+        <v>112800</v>
       </c>
       <c r="E76" s="60">
-        <f>D76*91.91%</f>
-        <v>143057.91499999998</v>
+        <f>D76</f>
+        <v>112800</v>
       </c>
       <c r="F76" s="49">
-        <f>D76*8.09%</f>
-        <v>12592.084999999999</v>
+        <v>0</v>
       </c>
       <c r="G76" s="66"/>
       <c r="H76" s="61"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="101" t="s">
-        <v>142</v>
-      </c>
-      <c r="B77" s="141"/>
-      <c r="C77" s="125"/>
-      <c r="D77" s="155">
-        <v>112800</v>
-      </c>
-      <c r="E77" s="60">
-        <f>D77</f>
-        <v>112800</v>
-      </c>
-      <c r="F77" s="49">
-        <v>0</v>
-      </c>
-      <c r="G77" s="66"/>
-      <c r="H77" s="61"/>
-    </row>
-    <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="118" t="s">
+    <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="B78" s="118"/>
-      <c r="C78" s="118"/>
-      <c r="D78" s="33">
-        <f>SUM(D75:D77)</f>
+      <c r="B77" s="118"/>
+      <c r="C77" s="118"/>
+      <c r="D77" s="33">
+        <f>SUM(D74:D76)</f>
         <v>520650</v>
       </c>
-      <c r="E78" s="33">
-        <f>SUM(E75:E77)</f>
+      <c r="E77" s="33">
+        <f>SUM(E74:E76)</f>
         <v>487654.93499999994</v>
       </c>
-      <c r="F78" s="33">
-        <f>SUM(F75:F77)</f>
+      <c r="F77" s="33">
+        <f>SUM(F74:F76)</f>
         <v>32995.065000000002</v>
       </c>
-      <c r="G78" s="34">
-        <f>E78+F78</f>
+      <c r="G77" s="34">
+        <f>E77+F77</f>
         <v>520649.99999999994</v>
       </c>
-      <c r="H78" s="61" t="str">
-        <f>IF(D78=G78, "", "Error")</f>
+      <c r="H77" s="61" t="str">
+        <f>IF(D77=G77, "", "Error")</f>
         <v/>
       </c>
-      <c r="J78" s="34"/>
+      <c r="J77" s="34"/>
+    </row>
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="79"/>
+      <c r="B78" s="79"/>
+      <c r="C78" s="79"/>
+      <c r="D78" s="104"/>
+      <c r="E78" s="39"/>
+      <c r="F78" s="3"/>
+      <c r="H78" s="61"/>
     </row>
     <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="79"/>
       <c r="B79" s="79"/>
       <c r="C79" s="79"/>
       <c r="D79" s="104"/>
-      <c r="E79" s="39"/>
+      <c r="E79" s="38"/>
       <c r="F79" s="3"/>
       <c r="H79" s="61"/>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="79"/>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="119" t="s">
+        <v>13</v>
+      </c>
       <c r="B80" s="79"/>
       <c r="C80" s="79"/>
       <c r="D80" s="104"/>
@@ -3277,595 +3247,587 @@
       <c r="F80" s="3"/>
       <c r="H80" s="61"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="119" t="s">
-        <v>13</v>
-      </c>
-      <c r="B81" s="79"/>
+        <v>14</v>
+      </c>
+      <c r="B81" s="79" t="s">
+        <v>127</v>
+      </c>
       <c r="C81" s="79"/>
-      <c r="D81" s="104"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="3"/>
+      <c r="D81" s="37">
+        <v>285700</v>
+      </c>
+      <c r="E81" s="60">
+        <f>D81*91.91%</f>
+        <v>262586.87</v>
+      </c>
+      <c r="F81" s="49">
+        <f>D81*8.09%</f>
+        <v>23113.13</v>
+      </c>
+      <c r="G81" t="s">
+        <v>112</v>
+      </c>
       <c r="H81" s="61"/>
     </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="119" t="s">
-        <v>14</v>
-      </c>
-      <c r="B82" s="79" t="s">
-        <v>127</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="B82" s="79"/>
       <c r="C82" s="79"/>
-      <c r="D82" s="155">
-        <v>285700</v>
+      <c r="D82" s="37">
+        <v>45000</v>
       </c>
       <c r="E82" s="60">
         <f>D82*91.91%</f>
-        <v>262586.87</v>
+        <v>41359.499999999993</v>
       </c>
       <c r="F82" s="49">
         <f>D82*8.09%</f>
-        <v>23113.13</v>
-      </c>
-      <c r="G82" t="s">
-        <v>112</v>
+        <v>3640.5</v>
       </c>
       <c r="H82" s="61"/>
+      <c r="J82" s="37"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="119" t="s">
-        <v>80</v>
-      </c>
+      <c r="A83" s="119"/>
       <c r="B83" s="79"/>
       <c r="C83" s="79"/>
-      <c r="D83" s="155">
-        <v>45000</v>
-      </c>
+      <c r="D83" s="104"/>
       <c r="E83" s="60">
         <f>D83*91.91%</f>
-        <v>41359.499999999993</v>
+        <v>0</v>
       </c>
       <c r="F83" s="49">
         <f>D83*8.09%</f>
-        <v>3640.5</v>
+        <v>0</v>
       </c>
       <c r="H83" s="61"/>
-      <c r="J83" s="37"/>
+      <c r="J83" s="34"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="119"/>
-      <c r="B84" s="79"/>
-      <c r="C84" s="79"/>
-      <c r="D84" s="104"/>
-      <c r="E84" s="60">
-        <f>D84*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F84" s="49">
-        <f>D84*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="H84" s="61"/>
+      <c r="A84" s="118"/>
+      <c r="B84" s="118"/>
+      <c r="C84" s="118"/>
+      <c r="D84" s="33">
+        <f>SUM(D81:D83)</f>
+        <v>330700</v>
+      </c>
+      <c r="E84" s="33">
+        <f>SUM(E81:E83)</f>
+        <v>303946.37</v>
+      </c>
+      <c r="F84" s="33">
+        <f>SUM(F81:F83)</f>
+        <v>26753.63</v>
+      </c>
+      <c r="G84" s="34">
+        <f>E84+F84</f>
+        <v>330700</v>
+      </c>
+      <c r="H84" s="61" t="str">
+        <f>IF(D84=G84, "", "Error")</f>
+        <v/>
+      </c>
       <c r="J84" s="34"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="118"/>
-      <c r="B85" s="118"/>
-      <c r="C85" s="118"/>
-      <c r="D85" s="33">
-        <f>SUM(D82:D84)</f>
-        <v>330700</v>
-      </c>
-      <c r="E85" s="33">
-        <f>SUM(E82:E84)</f>
-        <v>303946.37</v>
-      </c>
-      <c r="F85" s="33">
-        <f>SUM(F82:F84)</f>
-        <v>26753.63</v>
-      </c>
-      <c r="G85" s="34">
-        <f>E85+F85</f>
-        <v>330700</v>
-      </c>
-      <c r="H85" s="61" t="str">
-        <f>IF(D85=G85, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J85" s="34"/>
-    </row>
-    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="B85" s="79"/>
+      <c r="C85" s="79"/>
+      <c r="D85" s="37"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="3"/>
+      <c r="H85" s="61"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="119" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B86" s="79"/>
       <c r="C86" s="79"/>
-      <c r="D86" s="37"/>
-      <c r="E86" s="40"/>
-      <c r="F86" s="3"/>
+      <c r="D86" s="37">
+        <f>124723.15-7000</f>
+        <v>117723.15</v>
+      </c>
+      <c r="E86" s="60">
+        <f>D86*91.91%</f>
+        <v>108199.34716499998</v>
+      </c>
+      <c r="F86" s="49">
+        <f>D86*8.09%</f>
+        <v>9523.8028349999986</v>
+      </c>
       <c r="H86" s="61"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="119" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B87" s="79"/>
-      <c r="C87" s="79"/>
-      <c r="D87" s="158">
-        <v>114365.79</v>
+      <c r="C87" s="130"/>
+      <c r="D87" s="37">
+        <v>69000</v>
       </c>
       <c r="E87" s="60">
         <f>D87*91.91%</f>
-        <v>105113.59758899998</v>
+        <v>63417.899999999994</v>
       </c>
       <c r="F87" s="49">
         <f>D87*8.09%</f>
-        <v>9252.192411</v>
+        <v>5582.1</v>
       </c>
       <c r="H87" s="61"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="119" t="s">
-        <v>75</v>
-      </c>
-      <c r="B88" s="79"/>
-      <c r="C88" s="130"/>
-      <c r="D88" s="158">
-        <v>57500</v>
-      </c>
-      <c r="E88" s="60">
-        <f>D88*91.91%</f>
-        <v>52848.249999999993</v>
-      </c>
-      <c r="F88" s="49">
-        <f>D88*8.09%</f>
-        <v>4651.75</v>
-      </c>
-      <c r="H88" s="61"/>
+      <c r="A88" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" s="118"/>
+      <c r="C88" s="118"/>
+      <c r="D88" s="64">
+        <f>SUM(D86:D87)</f>
+        <v>186723.15</v>
+      </c>
+      <c r="E88" s="58">
+        <f t="shared" ref="E88:F88" si="24">SUM(E86:E87)</f>
+        <v>171617.24716499998</v>
+      </c>
+      <c r="F88" s="58">
+        <f t="shared" si="24"/>
+        <v>15105.902834999999</v>
+      </c>
+      <c r="G88" s="34">
+        <f>E88+F88</f>
+        <v>186723.14999999997</v>
+      </c>
+      <c r="H88" s="61" t="str">
+        <f>IF(D88=G88, "", "Error")</f>
+        <v/>
+      </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" s="118"/>
-      <c r="C89" s="118"/>
-      <c r="D89" s="64">
-        <f>SUM(D87:D88)</f>
-        <v>171865.78999999998</v>
-      </c>
-      <c r="E89" s="58">
-        <f t="shared" ref="E89:F89" si="22">SUM(E87:E88)</f>
-        <v>157961.84758899998</v>
-      </c>
-      <c r="F89" s="58">
-        <f t="shared" si="22"/>
-        <v>13903.942411</v>
-      </c>
-      <c r="G89" s="34">
-        <f>E89+F89</f>
-        <v>171865.78999999998</v>
-      </c>
-      <c r="H89" s="61" t="str">
-        <f>IF(D89=G89, "", "Error")</f>
+      <c r="A89" s="79"/>
+      <c r="B89" s="79"/>
+      <c r="C89" s="79"/>
+      <c r="D89" s="79"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="3"/>
+      <c r="H89" s="61"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="131" t="s">
+        <v>102</v>
+      </c>
+      <c r="B90" s="131"/>
+      <c r="C90" s="144"/>
+      <c r="D90" s="145"/>
+      <c r="E90" s="143">
+        <f>D90*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="51">
+        <f>D90*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G90" s="34">
+        <f>E90+F90</f>
+        <v>0</v>
+      </c>
+      <c r="H90" s="61" t="str">
+        <f>IF(D90=G90, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="79"/>
-      <c r="B90" s="79"/>
-      <c r="C90" s="79"/>
-      <c r="D90" s="79"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="3"/>
-      <c r="H90" s="61"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="131" t="s">
-        <v>102</v>
-      </c>
-      <c r="B91" s="131"/>
-      <c r="C91" s="145"/>
+    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="132"/>
+      <c r="B91" s="78"/>
+      <c r="C91" s="78"/>
       <c r="D91" s="146"/>
-      <c r="E91" s="144">
-        <f>D91*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F91" s="51">
-        <f>D91*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G91" s="34">
-        <f>E91+F91</f>
-        <v>0</v>
-      </c>
-      <c r="H91" s="61" t="str">
-        <f>IF(D91=G91, "", "Error")</f>
+      <c r="E91" s="147"/>
+      <c r="F91" s="147"/>
+      <c r="G91" s="63"/>
+      <c r="H91" s="61"/>
+    </row>
+    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="133" t="s">
+        <v>76</v>
+      </c>
+      <c r="B92" s="134"/>
+      <c r="C92" s="135"/>
+      <c r="D92" s="80">
+        <f>SUM(D90+D88+D84+D77+D70+D47+D32+D27+D42)</f>
+        <v>6858637.5199999996</v>
+      </c>
+      <c r="E92" s="59">
+        <f>SUM(E90+E88+E84+E77+E70+E47+E32+E27+E42)</f>
+        <v>6476775.4822319997</v>
+      </c>
+      <c r="F92" s="148">
+        <f>SUM(F27+F42+F47+F70+F77+F84+F88+F90)</f>
+        <v>381862.03776800004</v>
+      </c>
+      <c r="G92" s="34">
+        <f>E92+F92</f>
+        <v>6858637.5199999996</v>
+      </c>
+      <c r="H92" s="61" t="str">
+        <f>IF(D92=G92, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="132"/>
-      <c r="B92" s="78"/>
-      <c r="C92" s="78"/>
-      <c r="D92" s="147"/>
-      <c r="E92" s="148"/>
-      <c r="F92" s="148"/>
-      <c r="G92" s="63"/>
-      <c r="H92" s="61"/>
+      <c r="I92" s="76">
+        <f>D92-G92</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="133" t="s">
-        <v>76</v>
-      </c>
-      <c r="B93" s="134"/>
-      <c r="C93" s="135"/>
-      <c r="D93" s="80">
-        <f>SUM(D91+D89+D85+D78+D71+D47+D32+D27+D42)</f>
-        <v>6963780.1600000001</v>
-      </c>
-      <c r="E93" s="59">
-        <f>SUM(E91+E89+E85+E78+E71+E47+E32+E27+E42)</f>
-        <v>6561837.8005559994</v>
-      </c>
-      <c r="F93" s="149">
-        <f>SUM(F27+F42+F47+F71+F78+F85+F89+F91)</f>
-        <v>401942.359444</v>
-      </c>
-      <c r="G93" s="34">
-        <f>E93+F93</f>
-        <v>6963780.1599999992</v>
-      </c>
-      <c r="H93" s="61" t="str">
-        <f>IF(D93=G93, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I93" s="76">
-        <f>D93-G93</f>
-        <v>0</v>
-      </c>
+      <c r="A93" s="78"/>
+      <c r="B93" s="78"/>
+      <c r="C93" s="78"/>
+      <c r="D93" s="78"/>
+      <c r="E93" s="34"/>
     </row>
     <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="78"/>
-      <c r="B94" s="78"/>
-      <c r="C94" s="78"/>
+      <c r="A94" s="136" t="s">
+        <v>108</v>
+      </c>
+      <c r="B94" s="137"/>
+      <c r="C94" s="137"/>
       <c r="D94" s="78"/>
       <c r="E94" s="34"/>
     </row>
-    <row r="95" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="136" t="s">
-        <v>108</v>
-      </c>
-      <c r="B95" s="137"/>
-      <c r="C95" s="137"/>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+      <c r="C95" s="54"/>
       <c r="D95" s="78"/>
       <c r="E95" s="34"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="C96" s="54"/>
+      <c r="D96" s="78"/>
       <c r="E96" s="34"/>
     </row>
     <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="1"/>
-      <c r="C97" s="54"/>
+      <c r="A97" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B97" s="57"/>
+      <c r="C97" s="55">
+        <f>SUM(C95:C96)</f>
+        <v>0</v>
+      </c>
       <c r="E97" s="34"/>
     </row>
-    <row r="98" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="56" t="s">
-        <v>25</v>
-      </c>
-      <c r="B98" s="57"/>
-      <c r="C98" s="55">
-        <f>SUM(C96:C97)</f>
-        <v>0</v>
-      </c>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E98" s="34"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E99" s="34"/>
+      <c r="E99" s="52"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E100" s="52"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="180" t="s">
+      <c r="A100" s="174" t="s">
         <v>85</v>
       </c>
-      <c r="B101" s="181"/>
-      <c r="C101" s="181"/>
-      <c r="D101" s="181"/>
-      <c r="E101" s="73" t="s">
+      <c r="B100" s="175"/>
+      <c r="C100" s="175"/>
+      <c r="D100" s="175"/>
+      <c r="E100" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="F101" s="74" t="s">
+      <c r="F100" s="74" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A102" s="177"/>
-      <c r="B102" s="178"/>
-      <c r="C102" s="179"/>
+    <row r="101" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A101" s="171"/>
+      <c r="B101" s="172"/>
+      <c r="C101" s="173"/>
+      <c r="D101" s="37"/>
+      <c r="E101" s="60">
+        <f t="shared" ref="E101:E102" si="25">D101*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F101" s="49">
+        <f t="shared" ref="F101:F102" si="26">D101*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="176"/>
+      <c r="B102" s="177"/>
+      <c r="C102" s="178"/>
       <c r="D102" s="37"/>
       <c r="E102" s="60">
-        <f t="shared" ref="E102:E103" si="23">D102*91.91%</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F102" s="49">
-        <f t="shared" ref="F102:F103" si="24">D102*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="182"/>
-      <c r="B103" s="183"/>
-      <c r="C103" s="184"/>
-      <c r="D103" s="37"/>
-      <c r="E103" s="60">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="F103" s="49">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="174" t="s">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="168" t="s">
         <v>25</v>
       </c>
-      <c r="B104" s="175"/>
-      <c r="C104" s="176"/>
-      <c r="D104" s="72">
-        <f>SUM(D102:D103)</f>
-        <v>0</v>
-      </c>
-      <c r="E104" s="72">
-        <f>SUM(E102:E103)</f>
-        <v>0</v>
-      </c>
-      <c r="F104" s="72">
-        <f>SUM(F102:F103)</f>
-        <v>0</v>
-      </c>
-      <c r="H104" s="34">
-        <f>E104+F104</f>
-        <v>0</v>
-      </c>
-      <c r="I104" s="61" t="str">
-        <f>IF(D104=H104, "", "Error")</f>
+      <c r="B103" s="169"/>
+      <c r="C103" s="170"/>
+      <c r="D103" s="72">
+        <f>SUM(D101:D102)</f>
+        <v>0</v>
+      </c>
+      <c r="E103" s="72">
+        <f>SUM(E101:E102)</f>
+        <v>0</v>
+      </c>
+      <c r="F103" s="72">
+        <f>SUM(F101:F102)</f>
+        <v>0</v>
+      </c>
+      <c r="H103" s="34">
+        <f>E103+F103</f>
+        <v>0</v>
+      </c>
+      <c r="I103" s="61" t="str">
+        <f>IF(D103=H103, "", "Error")</f>
         <v/>
       </c>
     </row>
+    <row r="105" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E105" s="34"/>
+    </row>
     <row r="106" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E106" s="34"/>
+      <c r="A106" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B106" s="29">
+        <f>D92</f>
+        <v>6858637.5199999996</v>
+      </c>
     </row>
     <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="B107" s="29">
-        <f>D93</f>
-        <v>6963780.1600000001</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="30" t="s">
+      <c r="A107" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B108" s="31">
-        <f>D93-D91</f>
-        <v>6963780.1600000001</v>
-      </c>
+      <c r="B107" s="31">
+        <f>D92-D90</f>
+        <v>6858637.5199999996</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D108" s="158"/>
+      <c r="E108" s="158"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D109" s="164"/>
-      <c r="E109" s="164"/>
+      <c r="A109" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B109" s="10"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="158"/>
+      <c r="E109" s="158"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B110" s="10"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="164"/>
-      <c r="E110" s="164"/>
+      <c r="A110" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B110" s="5">
+        <v>12981485.379368611</v>
+      </c>
+      <c r="C110" s="13"/>
+      <c r="D110" s="158"/>
+      <c r="E110" s="158"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B111" s="5">
-        <v>12981485.379368611</v>
-      </c>
-      <c r="C111" s="13"/>
-      <c r="D111" s="164"/>
-      <c r="E111" s="164"/>
+      <c r="A111" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B111" s="23">
+        <f>PRORRATEO!G52</f>
+        <v>7986260.3999579996</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D111" s="158"/>
+      <c r="E111" s="158"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B112" s="23">
-        <f>PRORRATEO!G52</f>
-        <v>7986260.3999579996</v>
-      </c>
-      <c r="C112" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D112" s="164"/>
-      <c r="E112" s="164"/>
+        <v>87</v>
+      </c>
+      <c r="B112" s="75">
+        <f>-B107</f>
+        <v>-6858637.5199999996</v>
+      </c>
+      <c r="C112" s="11"/>
+      <c r="D112" s="158"/>
+      <c r="E112" s="158"/>
+      <c r="G112" s="37"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B113" s="75">
-        <f>-B108</f>
-        <v>-6963780.1600000001</v>
+        <f>-D103</f>
+        <v>0</v>
       </c>
       <c r="C113" s="11"/>
-      <c r="D113" s="164"/>
-      <c r="E113" s="164"/>
-      <c r="G113" s="37"/>
+      <c r="D113" s="158"/>
+      <c r="E113" s="158"/>
+      <c r="G113" s="43"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B114" s="75">
-        <f>-D104</f>
-        <v>0</v>
-      </c>
-      <c r="C114" s="11"/>
-      <c r="D114" s="164"/>
-      <c r="E114" s="164"/>
-      <c r="G114" s="43"/>
+        <f>-B120</f>
+        <v>-20000</v>
+      </c>
+      <c r="C114" s="15"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B115" s="75">
-        <f>-B121</f>
-        <v>-20000</v>
+        <v>91</v>
+      </c>
+      <c r="B115" s="24">
+        <f>-C97</f>
+        <v>0</v>
       </c>
       <c r="C115" s="15"/>
+      <c r="E115" s="34"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A116" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="B116" s="24">
-        <f>-C98</f>
-        <v>0</v>
-      </c>
-      <c r="C116" s="15"/>
-      <c r="E116" s="34"/>
+      <c r="A116" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B116" s="16">
+        <f>SUM(B110:B115)</f>
+        <v>14089108.259326611</v>
+      </c>
+      <c r="C116" s="62"/>
+      <c r="D116" s="34"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A117" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B117" s="16">
-        <f>SUM(B111:B116)</f>
-        <v>13983965.61932661</v>
-      </c>
-      <c r="C117" s="62"/>
-      <c r="D117" s="34"/>
+      <c r="A117" s="15"/>
+      <c r="C117" s="11"/>
+      <c r="D117" s="18"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A118" s="15"/>
       <c r="C118" s="11"/>
-      <c r="D118" s="18"/>
+      <c r="D118" s="34"/>
+      <c r="E118" s="76"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C119" s="11"/>
-      <c r="D119" s="34"/>
+      <c r="A119" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B119" s="86">
+        <v>-102694.54000000004</v>
+      </c>
+      <c r="C119" s="17"/>
+      <c r="D119" s="76"/>
       <c r="E119" s="76"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A120" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B120" s="86">
-        <v>-102694.54000000004</v>
+      <c r="F119" s="76"/>
+    </row>
+    <row r="120" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B120" s="24">
+        <v>20000</v>
       </c>
       <c r="C120" s="17"/>
       <c r="D120" s="76"/>
-      <c r="E120" s="76"/>
-      <c r="F120" s="76"/>
-    </row>
-    <row r="121" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B121" s="24">
-        <v>20000</v>
-      </c>
+      <c r="E120" s="81"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" s="12"/>
+      <c r="B121" s="75"/>
       <c r="C121" s="17"/>
-      <c r="D121" s="76"/>
-      <c r="E121" s="81"/>
+      <c r="E121" s="34"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="12"/>
       <c r="B122" s="75"/>
       <c r="C122" s="17"/>
+      <c r="D122" s="138"/>
       <c r="E122" s="34"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A123" s="12"/>
-      <c r="B123" s="75"/>
+      <c r="A123" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B123" s="27">
+        <f>SUM(B119:B122)</f>
+        <v>-82694.540000000037</v>
+      </c>
       <c r="C123" s="17"/>
-      <c r="D123" s="138"/>
-      <c r="E123" s="34"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A124" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B124" s="27">
-        <f>SUM(B120:B123)</f>
-        <v>-82694.540000000037</v>
-      </c>
-      <c r="C124" s="17"/>
+      <c r="C124" s="18"/>
+      <c r="D124" s="76"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C125" s="18"/>
-      <c r="D125" s="76"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B126" s="15"/>
-      <c r="C126" s="11"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N128" s="6"/>
+      <c r="B125" s="15"/>
+      <c r="C125" s="11"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N127" s="6"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B130" s="157"/>
+      <c r="C130" s="157"/>
+      <c r="D130" s="157"/>
+      <c r="E130" s="157"/>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B131" s="163"/>
-      <c r="C131" s="163"/>
-      <c r="D131" s="163"/>
-      <c r="E131" s="163"/>
+      <c r="B131" s="157"/>
+      <c r="C131" s="157"/>
+      <c r="D131" s="157"/>
+      <c r="E131" s="157"/>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B132" s="163"/>
-      <c r="C132" s="163"/>
-      <c r="D132" s="163"/>
-      <c r="E132" s="163"/>
+      <c r="B132" s="157"/>
+      <c r="C132" s="157"/>
+      <c r="D132" s="157"/>
+      <c r="E132" s="157"/>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B133" s="163"/>
-      <c r="C133" s="163"/>
-      <c r="D133" s="163"/>
-      <c r="E133" s="163"/>
+      <c r="B133" s="157"/>
+      <c r="C133" s="157"/>
+      <c r="D133" s="157"/>
+      <c r="E133" s="157"/>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B134" s="163"/>
-      <c r="C134" s="163"/>
-      <c r="D134" s="163"/>
-      <c r="E134" s="163"/>
-    </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B135" s="163"/>
-      <c r="C135" s="163"/>
-      <c r="D135" s="163"/>
-      <c r="E135" s="163"/>
+      <c r="B134" s="157"/>
+      <c r="C134" s="157"/>
+      <c r="D134" s="157"/>
+      <c r="E134" s="157"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B131:E135"/>
-    <mergeCell ref="D109:E114"/>
+    <mergeCell ref="B130:E134"/>
+    <mergeCell ref="D108:E113"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A100:D100"/>
     <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A66:C66"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A67:C67"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3897,44 +3859,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="203" t="str">
+      <c r="A1" s="198" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 18/06</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="205"/>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="200"/>
       <c r="K1" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="192">
-        <f>RESUMEN!D93</f>
-        <v>6963780.1600000001</v>
-      </c>
-      <c r="M1" s="193"/>
+      <c r="L1" s="189">
+        <f>RESUMEN!D92</f>
+        <v>6858637.5199999996</v>
+      </c>
+      <c r="M1" s="190"/>
       <c r="N1" s="91"/>
       <c r="O1" s="50">
         <f>L1*8.09%</f>
-        <v>563369.81494399998</v>
+        <v>554863.77536799992</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="206"/>
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="207"/>
-      <c r="H2" s="207"/>
-      <c r="I2" s="207"/>
-      <c r="J2" s="208"/>
+      <c r="A2" s="201"/>
+      <c r="B2" s="202"/>
+      <c r="C2" s="202"/>
+      <c r="D2" s="202"/>
+      <c r="E2" s="202"/>
+      <c r="F2" s="202"/>
+      <c r="G2" s="202"/>
+      <c r="H2" s="202"/>
+      <c r="I2" s="202"/>
+      <c r="J2" s="203"/>
       <c r="K2" s="92" t="s">
         <v>95</v>
       </c>
@@ -3946,42 +3908,42 @@
       <c r="N2" s="94"/>
       <c r="O2" s="50">
         <f>O1-K7-553-50-86-8</f>
-        <v>252249.59498599998</v>
+        <v>243743.55540999991</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="206"/>
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
-      <c r="I3" s="207"/>
-      <c r="J3" s="208"/>
+      <c r="A3" s="201"/>
+      <c r="B3" s="202"/>
+      <c r="C3" s="202"/>
+      <c r="D3" s="202"/>
+      <c r="E3" s="202"/>
+      <c r="F3" s="202"/>
+      <c r="G3" s="202"/>
+      <c r="H3" s="202"/>
+      <c r="I3" s="202"/>
+      <c r="J3" s="203"/>
       <c r="K3" s="92" t="s">
         <v>100</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="95">
-        <f>RESUMEN!D104</f>
+        <f>RESUMEN!D103</f>
         <v>0</v>
       </c>
       <c r="N3" s="96"/>
       <c r="O3" s="8"/>
     </row>
     <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="209"/>
-      <c r="B4" s="210"/>
-      <c r="C4" s="210"/>
-      <c r="D4" s="210"/>
-      <c r="E4" s="210"/>
-      <c r="F4" s="210"/>
-      <c r="G4" s="210"/>
-      <c r="H4" s="210"/>
-      <c r="I4" s="210"/>
-      <c r="J4" s="211"/>
+      <c r="A4" s="204"/>
+      <c r="B4" s="205"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="205"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="206"/>
       <c r="K4" s="97" t="s">
         <v>95</v>
       </c>
@@ -3996,64 +3958,64 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="196" t="s">
+      <c r="A5" s="186" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="212" t="s">
+      <c r="B5" s="207" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="196" t="s">
+      <c r="C5" s="186" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="201" t="s">
+      <c r="D5" s="196" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="196" t="s">
+      <c r="E5" s="186" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="196" t="s">
+      <c r="F5" s="186" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="196" t="s">
+      <c r="G5" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="198" t="s">
+      <c r="H5" s="193" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="201" t="s">
+      <c r="I5" s="196" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="194" t="s">
+      <c r="J5" s="191" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="194" t="s">
+      <c r="K5" s="191" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="194" t="s">
+      <c r="L5" s="191" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="194" t="s">
+      <c r="M5" s="191" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="194" t="s">
+      <c r="N5" s="191" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="197"/>
-      <c r="B6" s="213"/>
-      <c r="C6" s="197"/>
-      <c r="D6" s="214"/>
-      <c r="E6" s="197"/>
-      <c r="F6" s="197"/>
-      <c r="G6" s="197"/>
-      <c r="H6" s="199"/>
-      <c r="I6" s="202"/>
-      <c r="J6" s="200"/>
-      <c r="K6" s="195"/>
-      <c r="L6" s="200"/>
-      <c r="M6" s="195"/>
-      <c r="N6" s="195"/>
+      <c r="A6" s="187"/>
+      <c r="B6" s="208"/>
+      <c r="C6" s="187"/>
+      <c r="D6" s="209"/>
+      <c r="E6" s="187"/>
+      <c r="F6" s="187"/>
+      <c r="G6" s="187"/>
+      <c r="H6" s="194"/>
+      <c r="I6" s="197"/>
+      <c r="J6" s="195"/>
+      <c r="K6" s="192"/>
+      <c r="L6" s="195"/>
+      <c r="M6" s="192"/>
+      <c r="N6" s="192"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -4072,7 +4034,7 @@
       <c r="F7" s="19">
         <v>376162.55995799997</v>
       </c>
-      <c r="G7" s="159">
+      <c r="G7" s="154">
         <f>F7</f>
         <v>376162.55995799997</v>
       </c>
@@ -4116,7 +4078,7 @@
       <c r="F8" s="19">
         <v>187672.93683118254</v>
       </c>
-      <c r="G8" s="159">
+      <c r="G8" s="154">
         <v>190000</v>
       </c>
       <c r="H8" s="46">
@@ -4161,7 +4123,7 @@
       <c r="F9" s="19">
         <v>357849.60286759672</v>
       </c>
-      <c r="G9" s="160">
+      <c r="G9" s="105">
         <f>403750-G34</f>
         <v>357850</v>
       </c>
@@ -4207,7 +4169,7 @@
       <c r="F10" s="19">
         <v>241800</v>
       </c>
-      <c r="G10" s="159">
+      <c r="G10" s="154">
         <v>218000</v>
       </c>
       <c r="H10" s="46">
@@ -4252,7 +4214,7 @@
       <c r="F11" s="19">
         <v>291550</v>
       </c>
-      <c r="G11" s="159">
+      <c r="G11" s="154">
         <f>F11</f>
         <v>291550</v>
       </c>
@@ -4299,7 +4261,7 @@
       <c r="F12" s="19">
         <v>241400</v>
       </c>
-      <c r="G12" s="160">
+      <c r="G12" s="105">
         <f>F12</f>
         <v>241400</v>
       </c>
@@ -4345,7 +4307,7 @@
       <c r="F13" s="19">
         <v>291550.81741924176</v>
       </c>
-      <c r="G13" s="160">
+      <c r="G13" s="105">
         <f>341701-G50</f>
         <v>291551</v>
       </c>
@@ -4391,7 +4353,7 @@
       <c r="F14" s="19">
         <v>555195.10466666659</v>
       </c>
-      <c r="G14" s="159">
+      <c r="G14" s="154">
         <v>218322</v>
       </c>
       <c r="H14" s="46">
@@ -4479,7 +4441,7 @@
       <c r="F16" s="19">
         <v>241400.07982700004</v>
       </c>
-      <c r="G16" s="160">
+      <c r="G16" s="105">
         <f>283050-G49</f>
         <v>241400</v>
       </c>
@@ -4525,7 +4487,7 @@
       <c r="F17" s="19">
         <v>324891.38578511507</v>
       </c>
-      <c r="G17" s="159">
+      <c r="G17" s="154">
         <f>380749-G47-G48+14951</f>
         <v>306501</v>
       </c>
@@ -4571,7 +4533,7 @@
       <c r="F18" s="19">
         <v>261399.50379991793</v>
       </c>
-      <c r="G18" s="159">
+      <c r="G18" s="154">
         <f>309850-G51</f>
         <v>261400</v>
       </c>
@@ -4620,7 +4582,7 @@
       <c r="F19" s="19">
         <v>291549.81964850146</v>
       </c>
-      <c r="G19" s="160">
+      <c r="G19" s="105">
         <f>309578-G41</f>
         <v>263678</v>
       </c>
@@ -4666,7 +4628,7 @@
       <c r="F20" s="19">
         <v>241399.65585707471</v>
       </c>
-      <c r="G20" s="159">
+      <c r="G20" s="154">
         <f>283050-G38</f>
         <v>241400</v>
       </c>
@@ -4712,7 +4674,7 @@
       <c r="F21" s="19">
         <v>291549.9952936371</v>
       </c>
-      <c r="G21" s="159">
+      <c r="G21" s="154">
         <f>337450-G45</f>
         <v>291550</v>
       </c>
@@ -4758,7 +4720,7 @@
       <c r="F22" s="19">
         <v>241400</v>
       </c>
-      <c r="G22" s="159">
+      <c r="G22" s="154">
         <f>F22</f>
         <v>241400</v>
       </c>
@@ -4804,7 +4766,7 @@
       <c r="F23" s="19">
         <v>290748.66790342226</v>
       </c>
-      <c r="G23" s="160">
+      <c r="G23" s="105">
         <f>335000-G46</f>
         <v>292500</v>
       </c>
@@ -4850,7 +4812,7 @@
       <c r="F24" s="19">
         <v>240835.37342107471</v>
       </c>
-      <c r="G24" s="159">
+      <c r="G24" s="154">
         <f>290000-G37</f>
         <v>248350</v>
       </c>
@@ -4896,7 +4858,7 @@
       <c r="F25" s="19">
         <v>275750.79666666669</v>
       </c>
-      <c r="G25" s="160">
+      <c r="G25" s="105">
         <v>292296.84000000003</v>
       </c>
       <c r="H25" s="46">
@@ -4944,7 +4906,7 @@
       <c r="F26" s="19">
         <v>-2243661.3406672962</v>
       </c>
-      <c r="G26" s="160">
+      <c r="G26" s="105">
         <f>-G30-G31-G36</f>
         <v>-135150</v>
       </c>
@@ -4952,8 +4914,8 @@
         <f t="shared" si="0"/>
         <v>-2108511.3406672962</v>
       </c>
-      <c r="I26" s="150" t="s">
-        <v>146</v>
+      <c r="I26" s="149" t="s">
+        <v>145</v>
       </c>
       <c r="J26" s="19">
         <f t="shared" si="2"/>
@@ -4990,7 +4952,7 @@
       <c r="F27" s="19">
         <v>500650.37128526531</v>
       </c>
-      <c r="G27" s="159">
+      <c r="G27" s="154">
         <f>600000-G39-G40</f>
         <v>501400</v>
       </c>
@@ -5037,7 +4999,7 @@
       <c r="F28" s="19">
         <v>499341.17449320736</v>
       </c>
-      <c r="G28" s="159">
+      <c r="G28" s="154">
         <f>600000-G32-G33</f>
         <v>509900</v>
       </c>
@@ -5083,7 +5045,7 @@
       <c r="F29" s="19">
         <v>1129090.7461941019</v>
       </c>
-      <c r="G29" s="160">
+      <c r="G29" s="105">
         <f>1428000-G42-G43-G44</f>
         <v>1154300</v>
       </c>
@@ -5129,7 +5091,7 @@
       <c r="F30" s="19">
         <v>45900.000000000007</v>
       </c>
-      <c r="G30" s="159">
+      <c r="G30" s="154">
         <f>F30</f>
         <v>45900.000000000007</v>
       </c>
@@ -5173,7 +5135,7 @@
       <c r="F31" s="19">
         <v>46750</v>
       </c>
-      <c r="G31" s="159">
+      <c r="G31" s="154">
         <f>F31</f>
         <v>46750</v>
       </c>
@@ -5217,7 +5179,7 @@
       <c r="F32" s="19">
         <v>38250</v>
       </c>
-      <c r="G32" s="159">
+      <c r="G32" s="154">
         <f>F32</f>
         <v>38250</v>
       </c>
@@ -5261,7 +5223,7 @@
       <c r="F33" s="19">
         <v>51850</v>
       </c>
-      <c r="G33" s="159">
+      <c r="G33" s="154">
         <f t="shared" ref="G33" si="5">F33</f>
         <v>51850</v>
       </c>
@@ -5305,7 +5267,7 @@
       <c r="F34" s="19">
         <v>45900.000000000007</v>
       </c>
-      <c r="G34" s="159">
+      <c r="G34" s="154">
         <f>F34</f>
         <v>45900.000000000007</v>
       </c>
@@ -5390,7 +5352,7 @@
       <c r="F36" s="19">
         <v>42500</v>
       </c>
-      <c r="G36" s="159">
+      <c r="G36" s="154">
         <f>F36</f>
         <v>42500</v>
       </c>
@@ -5434,7 +5396,7 @@
       <c r="F37" s="19">
         <v>41650</v>
       </c>
-      <c r="G37" s="159">
+      <c r="G37" s="154">
         <f t="shared" ref="G37:G41" si="6">F37</f>
         <v>41650</v>
       </c>
@@ -5478,7 +5440,7 @@
       <c r="F38" s="19">
         <v>41650</v>
       </c>
-      <c r="G38" s="159">
+      <c r="G38" s="154">
         <f t="shared" si="6"/>
         <v>41650</v>
       </c>
@@ -5522,7 +5484,7 @@
       <c r="F39" s="19">
         <v>50150</v>
       </c>
-      <c r="G39" s="159">
+      <c r="G39" s="154">
         <f t="shared" si="6"/>
         <v>50150</v>
       </c>
@@ -5566,7 +5528,7 @@
       <c r="F40" s="19">
         <v>48450</v>
       </c>
-      <c r="G40" s="159">
+      <c r="G40" s="154">
         <f t="shared" si="6"/>
         <v>48450</v>
       </c>
@@ -5610,7 +5572,7 @@
       <c r="F41" s="19">
         <v>45900.000000000007</v>
       </c>
-      <c r="G41" s="159">
+      <c r="G41" s="154">
         <f t="shared" si="6"/>
         <v>45900.000000000007</v>
       </c>
@@ -5654,7 +5616,7 @@
       <c r="F42" s="19">
         <v>93500</v>
       </c>
-      <c r="G42" s="159">
+      <c r="G42" s="154">
         <f>F42</f>
         <v>93500</v>
       </c>
@@ -5698,7 +5660,7 @@
       <c r="F43" s="19">
         <v>76500</v>
       </c>
-      <c r="G43" s="159">
+      <c r="G43" s="154">
         <f>F43</f>
         <v>76500</v>
       </c>
@@ -5726,7 +5688,7 @@
       </c>
       <c r="P43" s="34">
         <f>L1-K52</f>
-        <v>-412132.39995799866</v>
+        <v>-517275.03995799925</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -5746,7 +5708,7 @@
       <c r="F44" s="19">
         <v>103700</v>
       </c>
-      <c r="G44" s="159">
+      <c r="G44" s="154">
         <f>F44</f>
         <v>103700</v>
       </c>
@@ -5790,7 +5752,7 @@
       <c r="F45" s="19">
         <v>45900.000000000007</v>
       </c>
-      <c r="G45" s="159">
+      <c r="G45" s="154">
         <f t="shared" ref="G45" si="7">F45</f>
         <v>45900.000000000007</v>
       </c>
@@ -5834,7 +5796,7 @@
       <c r="F46" s="19">
         <v>42500</v>
       </c>
-      <c r="G46" s="159">
+      <c r="G46" s="154">
         <f t="shared" ref="G46:G51" si="8">F46</f>
         <v>42500</v>
       </c>
@@ -5881,7 +5843,7 @@
       <c r="F47" s="19">
         <v>45050</v>
       </c>
-      <c r="G47" s="159">
+      <c r="G47" s="154">
         <f t="shared" si="8"/>
         <v>45050</v>
       </c>
@@ -5930,7 +5892,7 @@
       <c r="F48" s="19">
         <v>44149</v>
       </c>
-      <c r="G48" s="159">
+      <c r="G48" s="154">
         <f t="shared" si="8"/>
         <v>44149</v>
       </c>
@@ -5975,7 +5937,7 @@
       <c r="F49" s="19">
         <v>41650</v>
       </c>
-      <c r="G49" s="159">
+      <c r="G49" s="154">
         <f t="shared" si="8"/>
         <v>41650</v>
       </c>
@@ -6019,7 +5981,7 @@
       <c r="F50" s="19">
         <v>50150</v>
       </c>
-      <c r="G50" s="160">
+      <c r="G50" s="105">
         <f t="shared" si="8"/>
         <v>50150</v>
       </c>
@@ -6063,7 +6025,7 @@
       <c r="F51" s="19">
         <v>48450</v>
       </c>
-      <c r="G51" s="159">
+      <c r="G51" s="154">
         <f t="shared" si="8"/>
         <v>48450</v>
       </c>
@@ -6134,36 +6096,36 @@
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="53">
         <f>K52-L1</f>
-        <v>412132.39995799866</v>
+        <v>517275.03995799925</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="215"/>
-      <c r="D54" s="215"/>
-      <c r="E54" s="215"/>
-      <c r="F54" s="215"/>
-      <c r="G54" s="215"/>
-      <c r="H54" s="215"/>
-      <c r="I54" s="215"/>
-      <c r="J54" s="215"/>
-      <c r="K54" s="215"/>
-      <c r="L54" s="215"/>
-      <c r="M54" s="215"/>
-      <c r="N54" s="215"/>
+      <c r="C54" s="188"/>
+      <c r="D54" s="188"/>
+      <c r="E54" s="188"/>
+      <c r="F54" s="188"/>
+      <c r="G54" s="188"/>
+      <c r="H54" s="188"/>
+      <c r="I54" s="188"/>
+      <c r="J54" s="188"/>
+      <c r="K54" s="188"/>
+      <c r="L54" s="188"/>
+      <c r="M54" s="188"/>
+      <c r="N54" s="188"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="215"/>
-      <c r="D55" s="215"/>
-      <c r="E55" s="215"/>
-      <c r="F55" s="215"/>
-      <c r="G55" s="215"/>
-      <c r="H55" s="215"/>
-      <c r="I55" s="215"/>
-      <c r="J55" s="215"/>
-      <c r="K55" s="215"/>
-      <c r="L55" s="215"/>
-      <c r="M55" s="215"/>
-      <c r="N55" s="215"/>
+      <c r="C55" s="188"/>
+      <c r="D55" s="188"/>
+      <c r="E55" s="188"/>
+      <c r="F55" s="188"/>
+      <c r="G55" s="188"/>
+      <c r="H55" s="188"/>
+      <c r="I55" s="188"/>
+      <c r="J55" s="188"/>
+      <c r="K55" s="188"/>
+      <c r="L55" s="188"/>
+      <c r="M55" s="188"/>
+      <c r="N55" s="188"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="70"/>
@@ -6180,107 +6142,111 @@
       <c r="N56" s="70"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="215" t="s">
+      <c r="C57" s="188" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="215"/>
-      <c r="E57" s="215"/>
-      <c r="F57" s="215"/>
-      <c r="G57" s="215"/>
-      <c r="H57" s="215"/>
-      <c r="I57" s="215"/>
-      <c r="J57" s="215"/>
-      <c r="K57" s="215"/>
-      <c r="L57" s="215"/>
-      <c r="M57" s="215"/>
-      <c r="N57" s="215"/>
+      <c r="D57" s="188"/>
+      <c r="E57" s="188"/>
+      <c r="F57" s="188"/>
+      <c r="G57" s="188"/>
+      <c r="H57" s="188"/>
+      <c r="I57" s="188"/>
+      <c r="J57" s="188"/>
+      <c r="K57" s="188"/>
+      <c r="L57" s="188"/>
+      <c r="M57" s="188"/>
+      <c r="N57" s="188"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="215"/>
-      <c r="D58" s="215"/>
-      <c r="E58" s="215"/>
-      <c r="F58" s="215"/>
-      <c r="G58" s="215"/>
-      <c r="H58" s="215"/>
-      <c r="I58" s="215"/>
-      <c r="J58" s="215"/>
-      <c r="K58" s="215"/>
-      <c r="L58" s="215"/>
-      <c r="M58" s="215"/>
-      <c r="N58" s="215"/>
+      <c r="C58" s="188"/>
+      <c r="D58" s="188"/>
+      <c r="E58" s="188"/>
+      <c r="F58" s="188"/>
+      <c r="G58" s="188"/>
+      <c r="H58" s="188"/>
+      <c r="I58" s="188"/>
+      <c r="J58" s="188"/>
+      <c r="K58" s="188"/>
+      <c r="L58" s="188"/>
+      <c r="M58" s="188"/>
+      <c r="N58" s="188"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="215"/>
-      <c r="D59" s="215"/>
-      <c r="E59" s="215"/>
-      <c r="F59" s="215"/>
-      <c r="G59" s="215"/>
-      <c r="H59" s="215"/>
-      <c r="I59" s="215"/>
-      <c r="J59" s="215"/>
-      <c r="K59" s="215"/>
-      <c r="L59" s="215"/>
-      <c r="M59" s="215"/>
-      <c r="N59" s="215"/>
+      <c r="C59" s="188"/>
+      <c r="D59" s="188"/>
+      <c r="E59" s="188"/>
+      <c r="F59" s="188"/>
+      <c r="G59" s="188"/>
+      <c r="H59" s="188"/>
+      <c r="I59" s="188"/>
+      <c r="J59" s="188"/>
+      <c r="K59" s="188"/>
+      <c r="L59" s="188"/>
+      <c r="M59" s="188"/>
+      <c r="N59" s="188"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="215"/>
-      <c r="D60" s="215"/>
-      <c r="E60" s="215"/>
-      <c r="F60" s="215"/>
-      <c r="G60" s="215"/>
-      <c r="H60" s="215"/>
-      <c r="I60" s="215"/>
-      <c r="J60" s="215"/>
-      <c r="K60" s="215"/>
-      <c r="L60" s="215"/>
-      <c r="M60" s="215"/>
-      <c r="N60" s="215"/>
+      <c r="C60" s="188"/>
+      <c r="D60" s="188"/>
+      <c r="E60" s="188"/>
+      <c r="F60" s="188"/>
+      <c r="G60" s="188"/>
+      <c r="H60" s="188"/>
+      <c r="I60" s="188"/>
+      <c r="J60" s="188"/>
+      <c r="K60" s="188"/>
+      <c r="L60" s="188"/>
+      <c r="M60" s="188"/>
+      <c r="N60" s="188"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="215"/>
-      <c r="D61" s="215"/>
-      <c r="E61" s="215"/>
-      <c r="F61" s="215"/>
-      <c r="G61" s="215"/>
-      <c r="H61" s="215"/>
-      <c r="I61" s="215"/>
-      <c r="J61" s="215"/>
-      <c r="K61" s="215"/>
-      <c r="L61" s="215"/>
-      <c r="M61" s="215"/>
-      <c r="N61" s="215"/>
+      <c r="C61" s="188"/>
+      <c r="D61" s="188"/>
+      <c r="E61" s="188"/>
+      <c r="F61" s="188"/>
+      <c r="G61" s="188"/>
+      <c r="H61" s="188"/>
+      <c r="I61" s="188"/>
+      <c r="J61" s="188"/>
+      <c r="K61" s="188"/>
+      <c r="L61" s="188"/>
+      <c r="M61" s="188"/>
+      <c r="N61" s="188"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="215"/>
-      <c r="D62" s="215"/>
-      <c r="E62" s="215"/>
-      <c r="F62" s="215"/>
-      <c r="G62" s="215"/>
-      <c r="H62" s="215"/>
-      <c r="I62" s="215"/>
-      <c r="J62" s="215"/>
-      <c r="K62" s="215"/>
-      <c r="L62" s="215"/>
-      <c r="M62" s="215"/>
-      <c r="N62" s="215"/>
+      <c r="C62" s="188"/>
+      <c r="D62" s="188"/>
+      <c r="E62" s="188"/>
+      <c r="F62" s="188"/>
+      <c r="G62" s="188"/>
+      <c r="H62" s="188"/>
+      <c r="I62" s="188"/>
+      <c r="J62" s="188"/>
+      <c r="K62" s="188"/>
+      <c r="L62" s="188"/>
+      <c r="M62" s="188"/>
+      <c r="N62" s="188"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="215"/>
-      <c r="D63" s="215"/>
-      <c r="E63" s="215"/>
-      <c r="F63" s="215"/>
-      <c r="G63" s="215"/>
-      <c r="H63" s="215"/>
-      <c r="I63" s="215"/>
-      <c r="J63" s="215"/>
-      <c r="K63" s="215"/>
-      <c r="L63" s="215"/>
-      <c r="M63" s="215"/>
-      <c r="N63" s="215"/>
+      <c r="C63" s="188"/>
+      <c r="D63" s="188"/>
+      <c r="E63" s="188"/>
+      <c r="F63" s="188"/>
+      <c r="G63" s="188"/>
+      <c r="H63" s="188"/>
+      <c r="I63" s="188"/>
+      <c r="J63" s="188"/>
+      <c r="K63" s="188"/>
+      <c r="L63" s="188"/>
+      <c r="M63" s="188"/>
+      <c r="N63" s="188"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
@@ -6295,10 +6261,6 @@
     <mergeCell ref="A1:J4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
